--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0010.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0010.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Khi giải phóng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;, nếu Changli đang mang 4 lớp [Enflamement], cô sẽ tiêu hao toàn bộ lớp [Enflamement] để giải phóng &lt;color=Highlight&gt;Flaming Sacrifice&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là sát thương Resonance Skill.</t>
+          <t>Khi giải phóng &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt;, nếu Changli đang mang 4 lớp [Lửa Thiêu Đốt], cô sẽ tiêu hao toàn bộ lớp [Lửa Thiêu Đốt] để giải phóng &lt;color=Highlight&gt;Lễ Hiến Lửa&lt;/color&gt;, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;, được tính là DMG Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Changli: &lt;color=#d4bf5f&gt;Enhanced Heavy Attack&lt;/color&gt;</t>
+          <t>Changli: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -771,9 +771,9 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; lên mục tiêu gần đó, nhận 4 tầng [Enflamement] và bước vào &lt;color=Highlight&gt;Fiery Feather&lt;/color&gt;.
-&lt;size=40&gt;&lt;color=Title&gt;Fiery Feather&lt;/color&gt;&lt;/size&gt;
-Trong vòng 10 giây, nếu Changli tung ra Heavy Attack &lt;color=Highlight&gt;Flaming Sacrifice&lt;/color&gt;, Attack của cô sẽ tăng lên, sau đó &lt;color=Highlight&gt;Fiery Feather&lt;/color&gt; sẽ kết thúc.</t>
+          <t>Gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; lên mục tiêu gần đó, nhận 4 tầng [Enflamement] và bước vào &lt;color=Highlight&gt;Trạng Thái Lông Vũ Rực Lửa&lt;/color&gt;.
+&lt;size=40&gt;&lt;color=Title&gt;Trạng Thái Lông Vũ Rực Lửa&lt;/color&gt;&lt;/size&gt;
+Trong vòng 10 giây, nếu Changli tung ra Đòn Nặng &lt;color=Highlight&gt;Hy Sinh Lửa Đỏ&lt;/color&gt;, ATK của cô sẽ tăng lên, sau đó &lt;color=Highlight&gt;Trạng Thái Lông Vũ Rực Lửa&lt;/color&gt; sẽ kết thúc.</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Changli: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Changli: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Jinhsi: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Jinhsi: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Jinhsi: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Jinhsi: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Lao về phía trước và thực hiện các đòn tấn công liên tiếp gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Lao về phía trước và thực hiện các đòn tấn công liên tiếp gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Jinhsi: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Jinhsi: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Giai đoạn Kỹ năng Cơ bản 1</t>
+          <t>Kỹ Năng Cơ Bản Cấp 1</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Giai đoạn Kỹ năng Cơ bản 2</t>
+          <t>Kỹ Năng Cơ Bản Cấp 2</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Giai đoạn Kỹ năng Cơ bản 3</t>
+          <t>Kỹ Năng Cơ Bản Cấp 3</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Giai đoạn Kỹ năng Cơ bản 4</t>
+          <t>Kỹ Năng Cơ Bản Cấp 4</t>
         </is>
       </c>
     </row>
@@ -1685,8 +1685,8 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Sau khi Jinhsi sử dụng Basic Attack Stage 4 hoặc Kỹ Năng Giới Thiệu, kỹ năng Resonance &lt;color=Highlight&gt;Overflowing Radiance&lt;/color&gt; sẽ khả dụng trong 5 giây.
-Resonance Skill &lt;color=Highlight&gt;Overflowing Radiance&lt;/color&gt; gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và đưa Jinhsi vào trạng thái &lt;color=Highlight&gt;Incarnation&lt;/color&gt;.
+          <t>Sau khi Jinhsi sử dụng Đòn Cơ Bản Giai Đoạn 4 hoặc Kỹ Năng Giới Thiệu, kỹ năng Cộng Hưởng &lt;color=Highlight&gt;Ánh Sáng Tràn Trề&lt;/color&gt; sẽ khả dụng trong 5 giây.
+Resonance Skill &lt;color=Highlight&gt;Ánh Sáng Tràn Trề&lt;/color&gt; gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và đưa Jinhsi vào trạng thái &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt;.
 Có thể sử dụng khi đang bay.</t>
         </is>
       </c>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Jinhsi: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Jinhsi: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Incarnation&lt;/color&gt;, kỹ năng Resonance thay thế &lt;color=Highlight&gt;Crescent Divinity&lt;/color&gt; sẽ khả dụng. &lt;color=Highlight&gt;Crescent Divinity&lt;/color&gt; gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt;, kỹ năng Cộng Hưởng thay thế &lt;color=Highlight&gt;Crescent Divinity&lt;/color&gt; sẽ khả dụng. &lt;color=Highlight&gt;Crescent Divinity&lt;/color&gt; gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Jinhsi: &lt;color=#d4bf5f&gt;Forte Circuit&lt;/color&gt; - &lt;color=Highlight&gt;Incarnation&lt;/color&gt;</t>
+          <t>Jinhsi: &lt;color=#d4bf5f&gt;Hướng dẫn Forte Circuit&lt;/color&gt; - &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Incarnation&lt;/color&gt;, đòn &lt;color=Highlight&gt;"Incarnation: Heavy Attack"&lt;/color&gt; sẽ khả dụng. Tấn công mục tiêu trên không với chi phí Thể Lực, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt;, đòn &lt;color=Highlight&gt;Heavy Attack Thay Thế "Hóa Thân: Heavy Attack"&lt;/color&gt; sẽ khả dụng. Tấn công mục tiêu trên không với chi phí STA, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Jinhsi: &lt;color=#d4bf5f&gt;Forte Circuit&lt;/color&gt; - &lt;color=Highlight&gt;Incarnation&lt;/color&gt;</t>
+          <t>Jinhsi: &lt;color=#d4bf5f&gt;Hướng dẫn Forte Circuit&lt;/color&gt; - &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Incarnation&lt;/color&gt;, đòn &lt;color=Highlight&gt;"Incarnation: Heavy Attack"&lt;/color&gt; sẽ khả dụng. Tấn công mục tiêu trên không với chi phí Thể Lực, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt;, đòn &lt;color=Highlight&gt;Heavy Attack Thay Thế "Hóa Thân: Heavy Attack"&lt;/color&gt; sẽ khả dụng. Tấn công mục tiêu trên không với chi phí STA, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Jinhsi: &lt;color=#d4bf5f&gt;Forte Circuit&lt;/color&gt; - &lt;color=Highlight&gt;Incarnation&lt;/color&gt;</t>
+          <t>Jinhsi: &lt;color=#d4bf5f&gt;Hướng dẫn Forte Circuit&lt;/color&gt; - &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2340,10 +2340,10 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Sau Giai đoạn 4 của &lt;color=Highlight&gt;Incarnation: Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Incarnation&lt;/color&gt; kết thúc và Jinhsi nhận được &lt;color=Highlight&gt;Ordination Glow&lt;/color&gt;.
-Khi ở trạng thái &lt;color=Highlight&gt;Ordination Glow&lt;/color&gt;, Basic Attack sẽ được thay thế bằng Heavy Attack &lt;color=Highlight&gt;"Incarnation: Heavy Attack"&lt;/color&gt; khi ở trên không. Tấn công mục tiêu giữa không trung bằng cách tiêu hao STA, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Resonance Skill được thay thế bằng Resonance Skill &lt;color=Highlight&gt;Illuminous Epiphany&lt;/color&gt;. Phóng ra &lt;color=Highlight&gt;Solar Flare&lt;/color&gt; và kích nổ thành &lt;color=Highlight&gt;Stella Glamour&lt;/color&gt; sau một khoảng thời gian ngắn.
-Sau khi sử dụng Resonance Skill &lt;color=Highlight&gt;Illuminous Epiphany&lt;/color&gt;, Jinhsi nhận được &lt;color=Highlight&gt;Unison&lt;/color&gt;. Khi Jinhsi có &lt;color=Highlight&gt;Unison&lt;/color&gt;, chuyển đổi sang Resonators khác sẽ loại bỏ &lt;color=Highlight&gt;Unison&lt;/color&gt; của Jinhsi để kích hoạt Outro Skill của Jinhsi và Intro Skill của Resonators mới vào, kéo dài trong 5 giây. &lt;color=Highlight&gt;Unison&lt;/color&gt; sẽ được ưu tiên tiêu hao thay cho Concerto Energy khi Concerto Energy đã đầy.</t>
+          <t>Sau Giai đoạn 4 của &lt;color=Highlight&gt;Hóa Thân: Đòn Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt; kết thúc và Jinhsi nhận được &lt;color=Highlight&gt;Ánh Sáng Phụng Lệnh&lt;/color&gt;.
+Khi ở trạng thái &lt;color=Highlight&gt;Ánh Sáng Phụng Lệnh&lt;/color&gt;, Đòn Basic Attack sẽ được thay thế bằng Đòn Heavy Attack &lt;color=Highlight&gt;"Hóa Thân: Đòn Heavy Attack"&lt;/color&gt; khi ở trên không. Tấn công mục tiêu giữa không trung bằng cách tiêu hao STA, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+Resonance Skill được thay thế bằng Resonance Skill &lt;color=Highlight&gt;Giác Tỉnh Minh Triết&lt;/color&gt;. Phóng ra &lt;color=Highlight&gt;Tia Sáng Mặt Trời&lt;/color&gt; và kích nổ thành &lt;color=Highlight&gt;Hào Quang Stella&lt;/color&gt; sau một khoảng thời gian ngắn.
+Sau khi sử dụng Resonance Skill &lt;color=Highlight&gt;Giác Tỉnh Minh Triết&lt;/color&gt;, Jinhsi nhận được &lt;color=Highlight&gt;Đồng Điệu&lt;/color&gt;. Khi Jinhsi có &lt;color=Highlight&gt;Đồng Điệu&lt;/color&gt;, chuyển đổi sang Resonator khác sẽ loại bỏ &lt;color=Highlight&gt;Đồng Điệu&lt;/color&gt; của Jinhsi để kích hoạt Kỹ Năng Outro của Jinhsi và Kỹ Năng Intro của Resonator mới vào, kéo dài trong 5 giây. &lt;color=Highlight&gt;Đồng Điệu&lt;/color&gt; sẽ được ưu tiên tiêu hao thay cho Concerto Energy khi Concerto Energy đã đầy.</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Giải phóng sức mạnh của khát vọng trái tim, gây &lt;color=Highlight&gt;Spectro DMG&lt;/color&gt;.
+          <t>Giải phóng sức mạnh của khát vọng trái tim, gây &lt;color=Highlight&gt;Sát Thương Spectro&lt;/color&gt;.
 Có thể sử dụng khi đang bay.</t>
         </is>
       </c>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Jinhsi: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Jinhsi: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Chệch: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Chệch: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Zhezhi: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Zhezhi: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Chệch: &lt;color=#d4bf5f&gt;Chain Heavy Attack&lt;/color&gt;</t>
+          <t>Chệch: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Liên Hoàn (Trên mặt đất)&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Chệch: &lt;color=#d4bf5f&gt;Chain Heavy Attack&lt;/color&gt;</t>
+          <t>Chệch: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Liên Hoàn (Giữa không trung)&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Zhezhi: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt; (Chạm)</t>
+          <t>Zhezhi: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt; (Chạm)</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Zhezhi: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt; (Giữ)</t>
+          <t>Zhezhi: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt; (Giữ)</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Zhezhi: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt; (Trên không)</t>
+          <t>Zhezhi: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt; (Trên không)</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Zhezhi: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Zhezhi: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và hồi Phục Khí.</t>
+          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và hồi Phục Khí.</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện tối đa 2 đòn tấn công liên tiếp trên không, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và hồi phục Afflatus.</t>
+          <t>Tiêu hao STA để thực hiện tối đa 2 đòn tấn công liên tiếp trên không, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và hồi phục Afflatus.</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tung ra Heavy Attack vào mục tiêu, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; không làm reset chu kỳ Basic Attack. Nó phục hồi Afflatus.</t>
+          <t>Tiêu hao STA để tung ra Đòn Tấn Công Mạnh vào mục tiêu, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. &lt;color=Highlight&gt;Đòn Tấn Công Mạnh&lt;/color&gt; không làm reset chu kỳ Đòn Basic Attack. Nó phục hồi Afflatus.</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Giữ Basic Attack&lt;/color&gt; trong thời gian ngắn sau khi thực hiện &lt;color=Highlight&gt;Basic Attack 3&lt;/color&gt; để kích hoạt.</t>
+          <t>Giữ &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; trong thời gian ngắn sau khi thực hiện &lt;color=Highlight&gt;Basic Attack 3&lt;/color&gt; để kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Giữ Basic Attack&lt;/color&gt; khi đang &lt;color=Highlight&gt;trên không&lt;/color&gt; để sử dụng.</t>
+          <t>Giữ &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; khi đang &lt;color=Highlight&gt;ở trên không&lt;/color&gt; để sử dụng.</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Nhấn Resonance Skill để thi triển, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Nhấn Resonance Skill để thi triển, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Giữ Resonance Skill để thi triển, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Giữ Resonance Skill để thi triển, gây &lt;color=Ice&gt;Sát Thương Hệ Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Nhấn Resonance Skill để thi triển &lt;color=Highlight&gt;trên không&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Nhấn Resonance Skill để thi triển &lt;color=Highlight&gt;giữa không trung&lt;/color&gt;, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, hãy dùng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; rồi &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để triệu hồi 3 &lt;color=Highlight&gt;Phantasmic Imprints&lt;/color&gt;. Mỗi &lt;color=Highlight&gt;Phantasmic Imprint&lt;/color&gt; cho phép Zhezhi thi triển 1 &lt;color=Highlight&gt;Chain Resonance Skill&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Thanh Năng Lượng&lt;/color&gt; đầy, hãy dùng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; rồi &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để triệu hồi 3 &lt;color=Highlight&gt;Ảnh Phách&lt;/color&gt;. Mỗi &lt;color=Highlight&gt;Ảnh Phách&lt;/color&gt; cho phép Zhezhi thi triển 1 &lt;color=Highlight&gt;Resonance Skill Liên Kết&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; rồi dùng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để triệu hồi 3 &lt;color=Highlight&gt;Phantasmic Imprints&lt;/color&gt;. Mỗi &lt;color=Highlight&gt;Phantasmic Imprint&lt;/color&gt; cho phép Zhezhi sử dụng 1 &lt;color=Highlight&gt;Chain Resonance Skill&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt; đầy, giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; rồi dùng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; để triệu hồi 3 &lt;color=Highlight&gt;Ảnh Phách&lt;/color&gt;. Mỗi &lt;color=Highlight&gt;Ảnh Phách&lt;/color&gt; cho phép Zhezhi sử dụng 1 &lt;color=Highlight&gt;Resonance Skill Dây Chuyền&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Trong thời gian ngắn sau khi sử dụng &lt;color=Highlight&gt;Chain Resonance Skill&lt;/color&gt;, nếu Zhezhi có &lt;color=Highlight&gt;Afflatus&lt;/color&gt;, bạn có thể giữ &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Chain Heavy Attack&lt;/color&gt; và triệu hồi thêm một &lt;color=Highlight&gt;Phantasmic Imprint&lt;/color&gt;.</t>
+          <t>Trong thời gian ngắn sau khi sử dụng &lt;color=Highlight&gt;Resonance Skill Dây&lt;/color&gt;, nếu Zhezhi có &lt;color=Highlight&gt;Afflatus&lt;/color&gt;, bạn có thể giữ &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Đòn Heavy Attack Dây&lt;/color&gt; và triệu hồi thêm một &lt;color=Highlight&gt;Ấn Tượng Ảo Ảnh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Trong thời gian ngắn sau khi sử dụng &lt;color=Highlight&gt;Chain Resonance Skill&lt;/color&gt;, nếu Zhezhi có &lt;color=Highlight&gt;Afflatus&lt;/color&gt;, bạn có thể giữ &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Chain Heavy Attack&lt;/color&gt; và triệu hồi thêm một &lt;color=Highlight&gt;Phantasmic Imprint&lt;/color&gt;.</t>
+          <t>Trong thời gian ngắn sau khi sử dụng &lt;color=Highlight&gt;Resonance Skill Dây&lt;/color&gt;, nếu Zhezhi có &lt;color=Highlight&gt;Afflatus&lt;/color&gt;, bạn có thể giữ &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Đòn Heavy Attack Dây&lt;/color&gt; và triệu hồi thêm một &lt;color=Highlight&gt;Ấn Tượng Ảo Ảnh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Chain Resonance Skill&lt;/color&gt;</t>
+          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Chuỗi&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Chain Resonance Skill&lt;/color&gt;</t>
+          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Chuỗi trong Trạng Thái Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Chain Resonance Skill&lt;/color&gt;</t>
+          <t>Xiangli Yao: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Chuỗi trong Trạng Thái Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tung đòn Heavy Attack vào mục tiêu, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tung đòn Heavy Attack vào mục tiêu, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tấn công mục tiêu, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Khi Thanh Forte đầy, ngươi có thể sử dụng &lt;color=Highlight&gt;Chain Resonance Skill&lt;/color&gt;.</t>
+          <t>Khi Thanh Forte đầy, ngươi có thể sử dụng &lt;color=Highlight&gt;Resonance Skill Liên Kết&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4556,8 +4556,8 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sẽ hồi phục Thanh Forte khi trúng mục tiêu.
-Khi Thanh Forte đầy, bạn có thể sử dụng &lt;color=Highlight&gt;Chain Resonance Skill&lt;/color&gt;.</t>
+          <t>Sau khi sử dụng &lt;color=Highlight&gt;Giải Cộng Hưởng&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sẽ hồi phục Thanh Forte khi trúng mục tiêu.
+Khi Thanh Forte đầy, bạn có thể sử dụng &lt;color=Highlight&gt;Resonance Skill Chuỗi&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4623,8 +4623,8 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; sẽ hồi phục Thanh Forte khi trúng mục tiêu.
-Khi Thanh Forte đầy, bạn có thể sử dụng &lt;color=Highlight&gt;Chain Resonance Skill&lt;/color&gt;.</t>
+          <t>Sau khi sử dụng &lt;color=Highlight&gt;Giải Cộng Hưởng&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; sẽ hồi phục Thanh Forte khi trúng mục tiêu.
+Khi Thanh Forte đầy, bạn có thể sử dụng &lt;color=Highlight&gt;Resonance Skill Chuỗi&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Youhu: Hướng dẫn &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Youhu: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Cơ Bản&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Youhu: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Youhu: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Youhu: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Youhu: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ năng Cộng Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Youhu: Hướng dẫn &lt;color=#d4bf5f&gt;Chain Resonance Skill - Chime&lt;/color&gt;</t>
+          <t>Youhu: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill Liên Hoàn - Chime&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Youhu: &lt;color=#d4bf5f&gt;Chain Resonance Skill - Ruyi&lt;/color&gt;</t>
+          <t>Youhu: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ năng Cộng Hưởng Chuỗi - Ruyi&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Youhu: Hướng dẫn &lt;color=#d4bf5f&gt;Chain Resonance Skill - Ding&lt;/color&gt;</t>
+          <t>Youhu: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill Liên Hoàn - Ding&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Youhu: Hướng dẫn &lt;color=#d4bf5f&gt;Chain Resonance Skill - Mask&lt;/color&gt;</t>
+          <t>Youhu: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill Liên Hoàn - Mặt Nạ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Youhu: Hướng dẫn &lt;color=#d4bf5f&gt;Chain Heavy Attack&lt;/color&gt;</t>
+          <t>Youhu: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Nặng Liên Hoàn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Youhu: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Youhu: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Khôi phục Đồng Hồ Forte.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Khôi phục Đồng Hồ Forte.</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Tấn Công Lao Xuống, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Tấn Công Lao Xuống, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; chưa đầy, &lt;color=Highlight&gt;giữ Normal Attack&lt;/color&gt; để vào trạng thái &lt;color=Highlight&gt;Fortune Rolling&lt;/color&gt;, từ từ khôi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;. Khi Thanh Forte đầy trong trạng thái &lt;color=Highlight&gt;Fortune Rolling&lt;/color&gt;, &lt;color=Highlight&gt;release the Normal Attack button&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Frostfall&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt; chưa đầy, &lt;color=Highlight&gt;giữ Đòn Normal Attack&lt;/color&gt; để vào trạng thái &lt;color=Highlight&gt;Fortune Rolling&lt;/color&gt;, từ từ khôi phục &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt;. Khi Thanh Forte đầy trong trạng thái &lt;color=Highlight&gt;Fortune Rolling&lt;/color&gt;, &lt;color=Highlight&gt;thả nút Đòn Normal Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Frostfall&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Chạm để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, hồi phục HP cho tất cả Resonator gần đó và thực hiện &lt;color=Highlight&gt;Lucky Draw&lt;/color&gt; một lần. Chỉ có thể tồn tại tối đa một &lt;color=Highlight&gt;Antique&lt;/color&gt; cùng lúc, và &lt;color=Highlight&gt;Antique&lt;/color&gt; mới rút được sẽ thay thế cái hiện có.</t>
+          <t>Chạm để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;, hồi phục HP cho tất cả Cộng Hưởng Giả gần đó và thực hiện &lt;color=Highlight&gt;Rút Thăm May Mắn&lt;/color&gt; một lần. Chỉ có thể tồn tại tối đa một &lt;color=Highlight&gt;Đồ Cổ&lt;/color&gt; cùng lúc, và &lt;color=Highlight&gt;Đồ Cổ&lt;/color&gt; mới rút được sẽ thay thế cái hiện có.</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=Highlight&gt;Antique: Chime&lt;/color&gt;, &lt;color=Highlight&gt;tap&lt;/color&gt; để tung đòn tấn công bằng Chuông, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Chuông có thể làm giảm Vibration Strength của kẻ địch hiệu quả.</t>
+          <t>Dùng &lt;color=Highlight&gt;Cổ Vật: Chuông&lt;/color&gt;, &lt;color=Highlight&gt;nhấn&lt;/color&gt; để tung đòn tấn công bằng Chuông, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Chuông có thể làm giảm Độ Rung của kẻ địch hiệu quả.</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=Highlight&gt;Antique: Ruyi&lt;/color&gt;, &lt;color=Highlight&gt;tap&lt;/color&gt; để tung đòn tấn công vào kẻ địch phía trước, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Như Ý có hệ số sát thương tương đối cao.</t>
+          <t>Dùng &lt;color=Highlight&gt;Cổ Vật: Như Ý&lt;/color&gt;, &lt;color=Highlight&gt;nhấn&lt;/color&gt; để tung đòn tấn công vào kẻ địch phía trước, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Như Ý có hệ số DMG tương đối cao.</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=Highlight&gt;Antique: Ding&lt;/color&gt;, &lt;color=Highlight&gt;tap&lt;/color&gt; để nhảy lên Đỉnh và lao về phía trước, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Đỉnh có thể phá vỡ thế phòng thủ của kẻ địch hiệu quả.</t>
+          <t>Dùng &lt;color=Highlight&gt;Cổ Vật: Đỉnh&lt;/color&gt;, &lt;color=Highlight&gt;nhấn&lt;/color&gt; để nhảy lên Đỉnh và lao về phía trước, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Đỉnh có thể phá vỡ thế phòng thủ của kẻ địch hiệu quả.</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=Highlight&gt;Antique: Mask&lt;/color&gt;, &lt;color=Highlight&gt;tap&lt;/color&gt; để Dodgem Mask vào kẻ địch phía trước, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Mask có thể kéo lê kẻ địch theo quỹ đạo của nó.</t>
+          <t>Dùng &lt;color=Highlight&gt;Cổ Vật: Mặt Nạ&lt;/color&gt;, &lt;color=Highlight&gt;nhấn&lt;/color&gt; để ném Mặt Nạ vào kẻ địch phía trước, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Mặt Nạ có thể kéo lê kẻ địch theo quỹ đạo của nó.</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Khi có đủ 4 Tụ Ân, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Poetic Essence&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; (được tính là Sát Thương Kỹ Năng) và hồi phục HP cho tất cả Resonator ở gần.</t>
+          <t>Khi có đủ 4 Tụ Ân, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Thi Ca Bản Thể&lt;/color&gt;, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; (được tính là Sát Thương Kỹ Năng) và hồi phục HP cho tất cả Cộng Hưởng Giả ở gần.</t>
         </is>
       </c>
     </row>
@@ -5860,8 +5860,8 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Youhu Dodgem cuộn giấy về phía kẻ địch, tạo ra một vụ nổ &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; trong khu vực.
-Trên vụ nổ sẽ xuất hiện bốn nút bấm. &lt;color=Highlight&gt;Choose a button&lt;/color&gt; trong thời gian quy định để nhận được &lt;color=Highlight&gt;Antique&lt;/color&gt; tương ứng. Nếu không, bạn sẽ nhận được một &lt;color=Highlight&gt;Antique&lt;/color&gt; ngẫu nhiên.</t>
+          <t>Youhu ném cuộn giấy về phía kẻ địch, tạo ra một vụ nổ &lt;color=Ice&gt;DMG Glacio&lt;/color&gt; trong khu vực.
+Trên vụ nổ sẽ xuất hiện bốn nút bấm. &lt;color=Highlight&gt;Hãy chọn một nút&lt;/color&gt; trong thời gian quy định để nhận được &lt;color=Highlight&gt;Cổ Vật&lt;/color&gt; tương ứng. Nếu không, bạn sẽ nhận được một &lt;color=Highlight&gt;Cổ Vật&lt;/color&gt; ngẫu nhiên.</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Hướng Dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Chain Heavy Attack&lt;/color&gt;</t>
+          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Hướng Dẫn Heavy Attack Liên Hoàn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Hướng Dẫn Heavy Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Shorekeeper: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill - Mid-air&lt;/color&gt;</t>
+          <t>Shorekeeper: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill - Bay trên không&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Resonance Liberation - Stellarealm 1&lt;/color&gt;</t>
+          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Hướng Dẫn Giải Cứu Cộng Hưởng - Stellarealm 1&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Resonance Liberation - Stellarealm 2&lt;/color&gt;</t>
+          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Hướng Dẫn Giải Cứu Cộng Hưởng - Stellarealm 2&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Chain Intro Skill&lt;/color&gt;</t>
+          <t>Shorekeeper: &lt;color=#d4bf5f&gt;Hướng Dẫn Kỹ Năng Intro Liên Hoàn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và tạo ra 1 &lt;color=Highlight&gt;Collapsed Core&lt;/color&gt; với mỗi đòn đánh. Mỗi &lt;color=Highlight&gt;Collapsed Core&lt;/color&gt; sẽ biến thành &lt;color=Highlight&gt;Flare Star Butterfly&lt;/color&gt; sau 6 giây. Nếu đã có 5 &lt;color=Highlight&gt;Collapsed Cores&lt;/color&gt;, đòn &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; tiếp theo của Shorekeeper sẽ ngay lập tức biến 1 &lt;color=Highlight&gt;Collapsed Core&lt;/color&gt; thành &lt;color=Highlight&gt;Flare Star Butterfly&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và tạo ra 1 &lt;color=Highlight&gt;Lõi Sụp Đổ&lt;/color&gt; với mỗi đòn đánh. Mỗi &lt;color=Highlight&gt;Lõi Sụp Đổ&lt;/color&gt; sẽ biến thành &lt;color=Highlight&gt;Bướm Sao Bùng Cháy&lt;/color&gt; sau 6 giây. Nếu đã có 5 &lt;color=Highlight&gt;Lõi Sụp Đổ&lt;/color&gt;, đòn &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; tiếp theo của Shorekeeper sẽ ngay lập tức biến 1 &lt;color=Highlight&gt;Lõi Sụp Đổ&lt;/color&gt; thành &lt;color=Highlight&gt;Bướm Sao Bùng Cháy&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Khi Shorekeeper tích đủ 5 đoạn Data Thực Nghiệm, sử dụng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; sẽ tiêu hao toàn bộ để kéo các mục tiêu gần đó vào, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Đồng thời, mọi &lt;color=Highlight&gt;Collapsed Cores&lt;/color&gt; sinh ra sẽ lập tức hóa thành &lt;color=Highlight&gt;Flare Star Butterflies&lt;/color&gt;.</t>
+          <t>Khi Shorekeeper tích đủ 5 đoạn Dữ Liệu Thực Nghiệm, sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; sẽ tiêu hao toàn bộ để kéo các mục tiêu gần đó vào, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;. Đồng thời, mọi &lt;color=Highlight&gt;Lõi Sụp Đổ&lt;/color&gt; sinh ra sẽ lập tức hóa thành &lt;color=Highlight&gt;Bươm Bướm Sao Bừng Sáng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Khi Thanh Forte chưa đầy, giữ &lt;color=Highlight&gt;Normal Attack Button&lt;/color&gt; để chuyển sang &lt;color=Highlight&gt;Unbound Form&lt;/color&gt;, tiêu hao STA liên tục. Trong trạng thái này, Shorekeeper sẽ tự động thu thập các vật phẩm thực vật gần đó. Nhấn &lt;color=Highlight&gt;Normal Attack Button&lt;/color&gt; hoặc hết STA để thoát &lt;color=Highlight&gt;Unbound Form&lt;/color&gt;, nhận Data Thực Nghiệm và tạo ra &lt;color=Highlight&gt;Collapsed Cores&lt;/color&gt;.</t>
+          <t>Khi Thanh Forte chưa đầy, giữ &lt;color=Highlight&gt;Nút Normal Attack&lt;/color&gt; để chuyển sang &lt;color=Highlight&gt;Trạng Thái Tự Do&lt;/color&gt;, tiêu hao STA liên tục. Trong trạng thái này, Shorekeeper sẽ tự động thu thập các vật phẩm thực vật gần đó. Nhấn &lt;color=Highlight&gt;Nút Normal Attack&lt;/color&gt; hoặc hết STA để thoát &lt;color=Highlight&gt;Trạng Thái Tự Do&lt;/color&gt;, nhận Dữ Liệu Thực Nghiệm và tạo ra &lt;color=Highlight&gt;Lõi Sụp Đổ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống. Mỗi đòn đánh tạo ra 1 &lt;color=Highlight&gt;Collapsed Core&lt;/color&gt;. Nhấn nhanh &lt;color=Highlight&gt;Normal Attack Button&lt;/color&gt; sau Đòn Lao Xuống để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Tấn Công Lao Xuống. Mỗi đòn đánh tạo ra 1 &lt;color=Highlight&gt;Lõi Sụp Đổ&lt;/color&gt;. Nhấn nhanh &lt;color=Highlight&gt;Nút Normal Attack&lt;/color&gt; sau Tấn Công Lao Xuống để thực hiện &lt;color=Highlight&gt;Giai Đoạn Basic Attack 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Khi Shorekeeper tích đủ 5 đoạn Data Thực Nghiệm, sử dụng &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; sẽ tiêu hao toàn bộ để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Đồng thời, mọi &lt;color=Highlight&gt;Collapsed Cores&lt;/color&gt; sinh ra sẽ lập tức hóa thành &lt;color=Highlight&gt;Flare Star Butterflies&lt;/color&gt;. Sau đó, nhanh tay nhấn &lt;color=Highlight&gt;Normal Attack Button&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.</t>
+          <t>Khi Shorekeeper tích đủ 5 đoạn Dữ Liệu Thực Nghiệm, sử dụng &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không&lt;/color&gt; sẽ tiêu hao toàn bộ để gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;. Đồng thời, mọi &lt;color=Highlight&gt;Lõi Sụp Đổ&lt;/color&gt; sinh ra sẽ lập tức hóa thành &lt;color=Highlight&gt;Bươm Bướm Sao Bừng Sáng&lt;/color&gt;. Sau đó, nhanh tay nhấn &lt;color=Highlight&gt;Nút Normal Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Giai Đoạn 2 Đòn Basic Attack&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Restore HP cho tất cả Resonator trong đội và triệu hồi 5 &lt;color=Highlight&gt;Dim Star Butterflies&lt;/color&gt;, tự động truy đuổi và tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Hồi phục HP cho tất cả Cộng Hưởng Giả trong đội và triệu hồi 5 &lt;color=Highlight&gt;Bươm Bướm Sao Mờ&lt;/color&gt;, tự động truy đuổi và tấn công mục tiêu, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Tạo ra &lt;color=Highlight&gt;Outer Stellarealm&lt;/color&gt; để liên tục phục hồi HP cho Resonator đang hoạt động bên trong.</t>
+          <t>Tạo ra &lt;color=Highlight&gt;Vùng Hư Không Ngoài Sao&lt;/color&gt; để liên tục phục hồi HP cho Resonator đang hoạt động bên trong.</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Tất cả Resonator trong đội sẽ tăng Crit. Rate khi ở trong &lt;color=Highlight&gt;Inner Stellarealm&lt;/color&gt;. &lt;color=Highlight&gt;Inner Stellarealm&lt;/color&gt; bao gồm mọi hiệu ứng của &lt;color=Highlight&gt;Outer Stellarealm&lt;/color&gt;.</t>
+          <t>Tất cả Cộng Hưởng Giả trong đội sẽ tăng Crit. Rate khi ở trong &lt;color=Highlight&gt;Nội Vực Tinh Tú&lt;/color&gt;. &lt;color=Highlight&gt;Nội Vực Tinh Tú&lt;/color&gt; bao gồm mọi hiệu ứng của &lt;color=Highlight&gt;Ngoại Vực Tinh Tú&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Tất cả Resonator trong đội sẽ tăng Crit. DMG khi ở trong &lt;color=Highlight&gt;Supernal Stellarealm&lt;/color&gt;. &lt;color=Highlight&gt;Supernal Stellarealm&lt;/color&gt; bao gồm mọi hiệu ứng của &lt;color=Highlight&gt;Outer Stellarealm&lt;/color&gt; và &lt;color=Highlight&gt;Inner Stellarealm&lt;/color&gt;.</t>
+          <t>Tất cả Cộng Hưởng Giả trong đội sẽ tăng Crit. DMG khi ở trong &lt;color=Highlight&gt;Siêu Vực Tinh Tú&lt;/color&gt;. &lt;color=Highlight&gt;Siêu Vực Tinh Tú&lt;/color&gt; bao gồm mọi hiệu ứng của &lt;color=Highlight&gt;Ngoại Vực Tinh Tú&lt;/color&gt; và &lt;color=Highlight&gt;Nội Vực Tinh Tú&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Supernal Stellarealm&lt;/color&gt; tồn tại, Shorekeeper có thể dùng Intro Skill &lt;color=Highlight&gt;Discernment&lt;/color&gt; để kết thúc Tinh Vực hiện tại, phục hồi HP cho tất cả thành viên trong đội và gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; lên mục tiêu. Đòn tấn công này chắc chắn là một đòn Critical Hit gây Sát Thương Resonance Liberation.</t>
+          <t>Khi &lt;color=Highlight&gt;Siêu Thực Tinh Vực&lt;/color&gt; tồn tại, Shorekeeper có thể dùng Kỹ Năng Khởi Động &lt;color=Highlight&gt;Thấu Thị&lt;/color&gt; để kết thúc Tinh Vực hiện tại, phục hồi HP cho tất cả thành viên trong đội và gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; lên mục tiêu. Đòn tấn công này chắc chắn là một đòn Bạo Kích gây Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Camellya: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Camellya: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Camellya - Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill: Crimson Blossom&lt;/color&gt;</t>
+          <t>Camellya - &lt;color=#d4bf5f&gt;Resonance Skill: Hoa Đỏ Thắm&lt;/color&gt; Hướng Dẫn</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Camellya - Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill: Floral Ravage&lt;/color&gt;</t>
+          <t>Camellya - &lt;color=#d4bf5f&gt;Resonance Skill: Cơn Thịnh Nộ Hoa Lệ&lt;/color&gt; Hướng Dẫn</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Camellya: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Camellya: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống giữa không trung, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống giữa không trung, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu và bước vào &lt;color=Highlight&gt;Blossom Mode&lt;/color&gt;.</t>
+          <t>Tấn công mục tiêu và bước vào &lt;color=Highlight&gt;Chế Độ Nở Hoa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu và kết thúc &lt;color=Highlight&gt;Blossom Mode&lt;/color&gt;.</t>
+          <t>Tấn công mục tiêu và kết thúc &lt;color=Highlight&gt;Chế Độ Nở Hoa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Blossom Mode&lt;/color&gt; và thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Chế Độ Hoa Nở&lt;/color&gt; và thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp. Khi thực hiện &lt;color=Highlight&gt;Basic Attack 3&lt;/color&gt;, giữ &lt;color=Highlight&gt;Normal Attack Button&lt;/color&gt; để liên tục ra đòn vào mục tiêu.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp. Khi thực hiện &lt;color=Highlight&gt;Đòn Basic Attack 3&lt;/color&gt;, giữ &lt;color=Highlight&gt;Nút Normal Attack&lt;/color&gt; để liên tục ra đòn vào mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Blossom Mode&lt;/color&gt;, sử dụng Nhảy sẽ tấn công mục tiêu và kết thúc &lt;color=Highlight&gt;Blossom Mode&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Nở Hoa&lt;/color&gt;, sử dụng Nhảy sẽ tấn công mục tiêu và kết thúc &lt;color=Highlight&gt;Chế Độ Nở Hoa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Đòn tấn công này có thể thực hiện trên không nếu Camellya ở gần mặt đất.</t>
         </is>
       </c>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Lumi - &lt;color=#d4bf5f&gt;Red Light: Basic Attack&lt;/color&gt;</t>
+          <t>Lumi - &lt;color=#d4bf5f&gt;Ánh Sáng Đỏ: Hướng Dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Lumi - &lt;color=#d4bf5f&gt;Red Light: Heavy Attack&lt;/color&gt;</t>
+          <t>Lumi - &lt;color=#d4bf5f&gt;Hướng Dẫn: Tấn Công Mạnh (Đèn Đỏ)&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Lumi - &lt;color=#d4bf5f&gt;Red Light: Resonance Skill&lt;/color&gt;</t>
+          <t>Lumi - &lt;color=#d4bf5f&gt;Hướng Dẫn: Resonance Skill (Đèn Đỏ)&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Lumi - &lt;color=#d4bf5f&gt;Yellow Light: Resonance Skill&lt;/color&gt;</t>
+          <t>Lumi - &lt;color=#d4bf5f&gt;Hướng Dẫn: Resonance Skill (Đèn Vàng)&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Lumi - &lt;color=#d4bf5f&gt;Red Light: Chain Resonance Skill&lt;/color&gt;</t>
+          <t>Lumi - &lt;color=#d4bf5f&gt;Ánh Sáng Đỏ: Hướng Dẫn Resonance Skill Dây Chuyền&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Lumi - &lt;color=#d4bf5f&gt;Yellow Light: Basic Attack&lt;/color&gt;</t>
+          <t>Lumi - &lt;color=#d4bf5f&gt;Hướng Dẫn: Basic Attack (Đèn Vàng)&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Lumi - &lt;color=#d4bf5f&gt;Yellow Light: Chain Resonance Skill&lt;/color&gt;</t>
+          <t>Lumi - &lt;color=#d4bf5f&gt;Hướng Dẫn: Resonance Skill Liên Hoàn (Đèn Vàng)&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Lumi - &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Lumi - &lt;color=#d4bf5f&gt;Hướng Dẫn: Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9048,7 +9048,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Tiêu hao Thể Lực để thực hiện Đòn Hạ Bay giữa không trung, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Hạ Bay giữa không trung, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để bật lùi lại và tấn công mục tiêu trước khi chuyển sang &lt;color=Highlight&gt;Yellow Light Mode&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để bật lùi lại và tấn công mục tiêu trước khi chuyển sang &lt;color=Highlight&gt;Chế Độ Ánh Sáng Vàng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để vồ lấy và tấn công mục tiêu trước khi bước vào &lt;color=Highlight&gt;Red Light Mode&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để vồ lấy và tấn công mục tiêu trước khi bước vào &lt;color=Highlight&gt;Chế Độ Đèn Đỏ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu và bước vào &lt;color=Highlight&gt;Yellow Spotlight Mode&lt;/color&gt;, thay thế 6 &lt;color=Highlight&gt;Glitters&lt;/color&gt; tiếp theo bằng &lt;color=Highlight&gt;Glares&lt;/color&gt;.</t>
+          <t>Tấn công mục tiêu và bước vào &lt;color=Highlight&gt;Chế Độ Đèn Vàng&lt;/color&gt;, thay thế 6 &lt;color=Highlight&gt;Ánh Lấp Lánh&lt;/color&gt; tiếp theo bằng &lt;color=Highlight&gt;Ánh Chói Lòa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Summon Squeakie tấn công mục tiêu, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Triệu hồi Squeakie tấn công mục tiêu, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Dùng Dodge để vào &lt;color=Highlight&gt;Zoom Mode&lt;/color&gt;, tự động bắn &lt;color=Highlight&gt;Glitters&lt;/color&gt; vào mục tiêu.</t>
+          <t>Dùng Né Tránh để vào &lt;color=Highlight&gt;Chế Độ Phóng&lt;/color&gt;, tự động bắn &lt;color=Highlight&gt;Glitters&lt;/color&gt; vào mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu và bước vào &lt;color=Highlight&gt;Red Spotlight Mode&lt;/color&gt;, tăng cường 4 Basic Attack và/hoặc Heavy Attack tiếp theo.</t>
+          <t>Tấn công mục tiêu và bước vào &lt;color=Highlight&gt;Chế Độ Đèn Đỏ&lt;/color&gt;, tăng cường 4 Đòn Basic Attack và/hoặc Đòn Heavy Attack tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tấn công mục tiêu, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Carlotta khai hỏa 2 phát đầu, sau đó tiếp tục với 3 phát tăng cường, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và hồi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Carlotta khai hỏa 2 phát đầu, sau đó tiếp tục với 3 phát tăng cường, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và hồi &lt;color=Highlight&gt;Đồng Vị Phách&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Khi Carlotta nắm giữ &lt;color=Highlight&gt;Moldable Crystals&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; của cô sẽ trở thành &lt;color=Highlight&gt;Basic Attack - Necessary Measures&lt;/color&gt;.</t>
+          <t>Khi Carlotta nắm giữ &lt;color=Highlight&gt;Tinh Thể Dẻo&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; của cô sẽ trở thành &lt;color=Highlight&gt;Đòn Basic Attack - Biện Pháp Cần Thiết&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của Carlotta gây hiệu ứng &lt;color=Highlight&gt;Dispersion&lt;/color&gt; trong 1.5 giây. Kích hoạt lại &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; đúng lúc để lật mục tiêu và gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Tiêu hao &lt;color=Highlight&gt;Moldable Crystal&lt;/color&gt; sẽ hồi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của Carlotta gây hiệu ứng &lt;color=Highlight&gt;Phân Tán&lt;/color&gt; trong 1.5 giây. Kích hoạt lại &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; đúng lúc để lật mục tiêu và gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Tiêu hao &lt;color=Highlight&gt;Pha Lê Dẻo&lt;/color&gt; sẽ hồi phục &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Thực hiện Đòn Đòn Lao Xuống, tiêu hao STA và gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Thực hiện Đòn Tấn Công Lao Xuống, tiêu hao STA và gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; để khôi phục 3 &lt;color=Highlight&gt;Moldable Crystals&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; để khôi phục 3 &lt;color=Highlight&gt;Moldable Crystals&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, có thể sử dụng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt; đầy, có thể sử dụng &lt;color=Highlight&gt;Đòn Nặng Tăng Cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Enhance 4 đòn tấn công tiếp theo. Đòn thứ 5 sẽ giải phóng Resonance Liberation - &lt;color=Highlight&gt;Fatal Finale&lt;/color&gt;.</t>
+          <t>Tấn công mục tiêu, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Tăng cường 4 đòn tấn công tiếp theo. Đòn thứ 5 sẽ giải phóng Resonance Liberation - &lt;color=Highlight&gt;Kết Cục Chết Người&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Carlotta - Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Carlotta - Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Carlotta - Hướng dẫn &lt;color=#d4bf5f&gt;Special Heavy Attack&lt;/color&gt;</t>
+          <t>Carlotta - Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Mạnh Đặc Biệt&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Roccia: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Roccia: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Roccia: &lt;color=#d4bf5f&gt;Heavy Attack and Combo&lt;/color&gt;</t>
+          <t>Roccia: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh và Chuỗi Đòn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Roccia: &lt;color=#d4bf5f&gt;Resonance Skill and Combo&lt;/color&gt;</t>
+          <t>Roccia: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill và Chuỗi Đòn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Roccia: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Roccia: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Roccia: &lt;color=#d4bf5f&gt;Outro Skill&lt;/color&gt;</t>
+          <t>Roccia: &lt;color=#d4bf5f&gt;Hướng dẫn Outro Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. Restore &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. Hồi phục &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. Restore &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. Hồi phục &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tích lũy &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;. Khi đánh trúng kẻ địch với đủ &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;, Roccia sẽ bay lên không và kích hoạt &lt;color=Highlight&gt;Beyond Imagination&lt;/color&gt;. Ở trạng thái này, Roccia có thể tung &lt;color=Highlight&gt;Chain Plunging Attack&lt;/color&gt; nếu có đủ &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Giữ &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; để tích lũy &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt;. Khi đánh trúng kẻ địch với đủ &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt;, Roccia sẽ bay lên không và kích hoạt &lt;color=Highlight&gt;Vượt Qua Tưởng Tượng&lt;/color&gt;. Ở trạng thái này, Roccia có thể tung &lt;color=Highlight&gt;Đòn Lao Xuống Liên Hoàn&lt;/color&gt; nếu có đủ &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10803,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Kích hoạt để hút kẻ địch và đưa Roccia lên không trung, kích hoạt &lt;color=Highlight&gt;Beyond Imagination&lt;/color&gt;. Ở trạng thái này, Roccia có thể sử dụng &lt;color=Highlight&gt;Chain Plunging Attack&lt;/color&gt; nếu &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đủ.</t>
+          <t>Kích hoạt để hút kẻ địch và đưa Roccia lên không trung, kích hoạt &lt;color=Highlight&gt;Beyond Imagination&lt;/color&gt;. Ở trạng thái này, Roccia có thể sử dụng &lt;color=Highlight&gt;Chain Plunging Attack&lt;/color&gt; nếu &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt; đủ.</t>
         </is>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Kích hoạt để gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; lên kẻ địch.</t>
+          <t>Kích hoạt để gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, Roccia thay thế Công cụ của Resonator sắp xuất hiện bằng Magic Box để kéo kẻ địch về phía nó.</t>
+          <t>Khi Concerto Energy đạt tối đa, Roccia sẽ thay thế Tiện Ích của Resonator đang đến bằng Hộp Ma Thuật, kéo kẻ địch về phía nó.</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11063,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Basic Attack Trên Không Stage 1</t>
+          <t>Basic Attack Trên Không Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -11128,7 +11128,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Basic Attack Trên Không Stage 2</t>
+          <t>Basic Attack Trên Không Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Basic Attack Trên Không Stage 3</t>
+          <t>Basic Attack Trên Không Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Basic Attack Stage 4 Trên Không</t>
+          <t>Basic Attack Giai Đoạn 4 Trên Không</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Brant: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt; 1</t>
+          <t>Brant: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt; 1</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Brant: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt; 2</t>
+          <t>Brant: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt; 2</t>
         </is>
       </c>
     </row>
@@ -11648,7 +11648,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Brant: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt; 3</t>
+          <t>Brant: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt; 3</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Brant: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt; 1</t>
+          <t>Brant: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt; 1</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Brant: &lt;color=#d4bf5f&gt;Resonance Skill: Ascension&lt;/color&gt;</t>
+          <t>Brant: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill: Thăng Hoa&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Brant: &lt;color=#d4bf5f&gt;Resonance Skill: Landing&lt;/color&gt;</t>
+          <t>Brant: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ năng Cộng Hưởng: Hạ Cánh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Brant: &lt;color=#d4bf5f&gt;Enhanced Resonance Skill&lt;/color&gt;</t>
+          <t>Brant: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Brant: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Brant: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Brant: &lt;color=#d4bf5f&gt;Intro Skill and Resonance Liberation Combo&lt;/color&gt;</t>
+          <t>Brant: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ Năng Khởi Động và Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Khôi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;. Khôi phục &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Thực hiện 2 đòn tấn công liên tiếp và 1 Heavy Attack, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Thực hiện 2 đòn tấn công liên tiếp và 1 Đòn Nặng, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Thực hiện 4 đòn tấn công liên tiếp và 1 Heavy Attack, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Thực hiện 4 đòn tấn công liên tiếp và 1 Đòn Nặng, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Thực hiện 1 Heavy Attack gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Thực hiện 1 Đòn Heavy Attack gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Nhảy lên không trung và thực hiện 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Khôi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Nhảy lên không trung và thực hiện 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;. Khôi phục &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để nhảy lên không trung và thực hiện 4 đòn &lt;color=Highlight&gt;Tấn Công Trên Không&lt;/color&gt; liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để nhảy lên không trung và thực hiện 4 đòn &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Nhảy lên không trung. Giữ để thực hiện Đòn Mid-air Attack 1 &amp; 2, sau đó dùng Basic Attack để tiếp nối 2 giai đoạn tấn công còn lại, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Nhảy lên không trung. Giữ để thực hiện Đòn Tấn Công Giữa Không 1 &amp; 2, sau đó dùng Đòn Cơ Bản để tiếp nối 2 giai đoạn tấn công còn lại, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12558,7 +12558,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; chưa đầy, Brant sẽ thi triển &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trên mặt đất, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Khôi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt; chưa đầy, Brant sẽ thi triển &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trên mặt đất, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;. Khôi phục &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; chưa đầy, thi triển Resonance Skill giữa không trung sẽ gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Khôi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt; chưa đầy, thi triển Resonance Skill giữa không trung sẽ gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;. Khôi phục &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, Resonance Skill được tăng cường. Sử dụng Resonance Skill tăng cường sẽ tạo khiên và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Khôi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt; đầy, Resonance Skill được tăng cường. Sử dụng Resonance Skill tăng cường sẽ tạo khiên và gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;. Khôi phục &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi phục HP cho tất cả Resonators gần đó trong đội. Sau đó, bước vào trạng thái &lt;color=Highlight&gt;Aflame&lt;/color&gt;.
+          <t>Tấn công mục tiêu, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi phục HP cho tất cả Resonator gần đó trong đội. Sau đó, bước vào trạng thái &lt;color=Highlight&gt;Aflame&lt;/color&gt;.
 - Trong trạng thái này, Brant nạp &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; hiệu quả hơn.</t>
         </is>
       </c>
@@ -12820,7 +12820,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Brant thực hiện Intro Skill, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;. Sau khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; trên không, Brant bắt đầu chuỗi Mid-air Attack từ Stage 2 và nạp &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; hiệu quả hơn.</t>
+          <t>Brant thực hiện Kỹ Năng Khởi Động, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt;. Sau khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; trên không, Brant bắt đầu chuỗi Mid-air Attack từ Giai Đoạn 2 và nạp &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt; hiệu quả hơn.</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Phoebe: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Phoebe: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Phoebe: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Phoebe: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13015,7 +13015,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Phoebe: &lt;color=#d4bf5f&gt;Mid-air Heavy Attack&lt;/color&gt;</t>
+          <t>Phoebe: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh Giữa Không&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Phoebe: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Phoebe: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill 1&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Phoebe: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Phoebe: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill 2&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Phoebe: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Phoebe: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill 3&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Phoebe: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Phoebe: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13340,7 +13340,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Phoebe: &lt;color=#d4bf5f&gt;Concerto Skill&lt;/color&gt;</t>
+          <t>Phoebe: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ Năng Concerto&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Phoebe: &lt;color=#d4bf5f&gt;Outro Skill&lt;/color&gt;</t>
+          <t>Phoebe: &lt;color=#d4bf5f&gt;Hướng dẫn Outro Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Thực hiện 1 Heavy Attack gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Thực hiện 1 Đòn Heavy Attack gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Thực hiện 1 Đòn Lao Xuống gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Thực hiện 1 Đòn Lao Xuống gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Sử dụng Resonance Skill để triệu hồi Vòng Gương Ảnh. Khi Phoebe ở ngoài Vòng Gương Ảnh, tấn công Vòng Gương Ảnh bằng Basic Attack sẽ khiến đòn đánh dội lại bên trong vòng, gây thêm &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Sử dụng Resonance Skill để triệu hồi Vòng Gương Ảnh. Khi Phoebe ở ngoài Vòng Gương Ảnh, tấn công Vòng Gương Ảnh bằng Đòn Cơ Bản sẽ khiến đòn đánh dội lại bên trong vòng, gây thêm &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Khi chiếc nhẫn được triệu hồi bằng Resonance Skill, sử dụng lại Resonance Skill sẽ dịch chuyển Phoebe đến trung tâm chiếc nhẫn, nơi Basic Attack trở thành &lt;color=Highlight&gt;Chamuel's Star&lt;/color&gt;, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Khi chiếc nhẫn được triệu hồi bằng Resonance Skill, sử dụng lại Resonance Skill sẽ dịch chuyển Phoebe đến trung tâm chiếc nhẫn, nơi Đòn Cơ Bản trở thành &lt;color=Highlight&gt;Ngôi Sao Chamuel&lt;/color&gt;, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13860,7 +13860,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Khi Prayer đạt tối đa, giữ Normal Attack để bước vào trạng thái &lt;color=Highlight&gt;Absolution&lt;/color&gt;. Trong trạng thái này, giữ Normal Attack để thực hiện Heavy Attack &lt;color=Highlight&gt;Starflash&lt;/color&gt; sau 3 Basic Attack.</t>
+          <t>Khi Prayer đạt tối đa, giữ Normal Attack để bước vào trạng thái &lt;color=Highlight&gt;Absolution&lt;/color&gt;. Trong trạng thái này, giữ Normal Attack để thực hiện Đòn Heavy Attack &lt;color=Highlight&gt;Starflash&lt;/color&gt; sau 3 Đòn Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Khi Prayer đạt tối đa, giữ Resonance Skill để bước vào trạng thái &lt;color=Highlight&gt;Confession&lt;/color&gt;. Trong trạng thái này, giữ Normal Attack để thực hiện Heavy Attack &lt;color=Highlight&gt;Starflash&lt;/color&gt; sau 3 Basic Attack.</t>
+          <t>Khi Prayer đạt tối đa, giữ Resonance Skill để bước vào trạng thái &lt;color=Highlight&gt;Confession&lt;/color&gt;. Trong trạng thái này, giữ Normal Attack để thực hiện Đòn Heavy Attack &lt;color=Highlight&gt;Starflash&lt;/color&gt; sau 3 Đòn Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu và gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Nhận hiệu ứng tăng cường khác nhau tùy theo trạng thái hiện tại.</t>
+          <t>Tấn công mục tiêu và gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;. Nhận hiệu ứng tăng cường khác nhau tùy theo trạng thái hiện tại.</t>
         </is>
       </c>
     </row>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Cantarella: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Cantarella: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14185,7 +14185,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Cantarella: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Cantarella: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Heavy Attack I&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Cantarella: &lt;color=#d4bf5f&gt;Enhanced Heavy Attack&lt;/color&gt;
+          <t>Cantarella: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Nâng Cao&lt;/color&gt;
 Phần II</t>
         </is>
       </c>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Cantarella: &lt;color=#d4bf5f&gt;Enhanced Basic Attack&lt;/color&gt;</t>
+          <t>Cantarella: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Cantarella: Hướng dẫn &lt;color=#d4bf5f&gt;Enhanced Resonance Skill&lt;/color&gt; Nâng Cao</t>
+          <t>Cantarella: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt; Nâng Cao</t>
         </is>
       </c>
     </row>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Cantarella: Hướng dẫn Resonance Skill &lt;color=#d4bf5f&gt;Perception Drain&lt;/color&gt;</t>
+          <t>Cantarella: Hướng dẫn Resonance Skill &lt;color=#d4bf5f&gt;Hút Nhận Thức&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14577,7 +14577,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt; sẽ hồi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. &lt;color=Highlight&gt;Giai Đoạn 3 Đòn Basic Attack&lt;/color&gt; sẽ hồi &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14707,7 +14707,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và hồi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; và hồi &lt;color=Highlight&gt;Đồng Vị Khu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. Enter trạng thái &lt;color=Highlight&gt;Mirage&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. Vào trạng thái &lt;color=Highlight&gt;Ảo Ảnh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14903,8 +14903,8 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Mirage&lt;/color&gt;, {Cus:Ipt,Touch=chạm PC=nhấp chuột Gamepad=nhấn} hoặc giữ Normal Attack để thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Tiêu hao Trance để hồi phục Shiver và chữa lành cho tất cả Resonators trong đội ở gần.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Huyễn Ảnh&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=click Gamepad=press} hoặc giữ Đòn Normal Attack để thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+Tiêu hao Trance để hồi phục Shiver và chữa lành cho tất cả Resonator trong đội ở gần.</t>
         </is>
       </c>
     </row>
@@ -14970,8 +14970,8 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Mirage&lt;/color&gt;, tiêu hao Thể Lực để thực hiện Đòn Lao Xuống, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Tiêu hao Trance để hồi phục Shiver và chữa lành cho tất cả Resonators trong đội ở gần.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Huyễn Ảnh&lt;/color&gt;, tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+Tiêu hao Trance để hồi phục Shiver và chữa lành cho tất cả Resonator trong đội ở gần.</t>
         </is>
       </c>
     </row>
@@ -15037,8 +15037,8 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Mirage&lt;/color&gt;, sử dụng Nhảy sẽ tiêu hao Thể Lực để thực hiện Đòn Lao Xuống, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Tiêu hao Trance để hồi phục Shiver và chữa lành cho tất cả Resonators trong đội ở gần.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Huyễn Ảnh&lt;/color&gt;, sử dụng Nhảy sẽ tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+Tiêu hao Trance để hồi phục Shiver và chữa lành cho tất cả Resonator trong đội ở gần.</t>
         </is>
       </c>
     </row>
@@ -15103,7 +15103,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và đẩy mục tiêu vào trạng thái &lt;color=Highlight&gt;Hazy Dream&lt;/color&gt;.</t>
+          <t>Tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; và đẩy mục tiêu vào trạng thái &lt;color=Highlight&gt;Giấc Mơ Mơ Hồ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và hồi phục cho tất cả Resonators trong đội gần đó.</t>
+          <t>Tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; và hồi phục cho tất cả Resonator trong đội gần đó.</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và triệu hồi &lt;color=Highlight&gt;Dreamweavers&lt;/color&gt; để thực hiện Đòn Phối Hợp.</t>
+          <t>Tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; và triệu hồi &lt;color=Highlight&gt;Dreamweavers&lt;/color&gt; để thực hiện Đòn Phối Hợp.</t>
         </is>
       </c>
     </row>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Rover: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Rover: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15363,7 +15363,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Rover: &lt;color=#d4bf5f&gt;Enhanced Heavy Attack&lt;/color&gt;</t>
+          <t>Rover: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Resonance Skill&lt;/color&gt;</t>
+          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15623,7 +15623,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Rover: &lt;color=#d4bf5f&gt;Enhanced Resonance Skill&lt;/color&gt;</t>
+          <t>Rover: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và khôi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và khôi phục &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Kích hoạt kỹ năng để nhảy lên không trung, sau đó &lt;color=Highlight&gt;sử dụng Normal Attack&lt;/color&gt; ngay lập tức để tung ra &lt;color=Highlight&gt;Mid-air Attack cường hóa&lt;/color&gt;, hồi phục HP cho tất cả Resonators trong đội và khôi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Kích hoạt kỹ năng để nhảy lên không trung, sau đó &lt;color=Highlight&gt;dùng Đòn Normal Attack&lt;/color&gt; ngay lập tức để tung ra &lt;color=Highlight&gt;Đòn Mid-air Attack Nâng Cao&lt;/color&gt;, hồi phục HP cho tất cả Resonator trong đội và khôi phục &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Giữ Normal Attack&lt;/color&gt; ngay sau khi thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt; để nhảy lên không trung, rồi &lt;color=Highlight&gt;sử dụng Normal Attack&lt;/color&gt; ngay sau đó để tung ra &lt;color=Highlight&gt;Mid-air Attack cường hóa&lt;/color&gt;.</t>
+          <t>Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thực hiện &lt;color=Highlight&gt;Giai Đoạn 3 Basic Attack&lt;/color&gt; để nhảy lên không trung, rồi &lt;color=Highlight&gt;dùng Normal Attack&lt;/color&gt; ngay sau đó để tung ra &lt;color=Highlight&gt;Mid-air Attack Được Tăng Cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Khi ở trên không, sử dụng &lt;color=Highlight&gt;Mid-air Resonance Skill&lt;/color&gt; sẽ loại bỏ toàn bộ lớp Spectro Frazzle, Havoc Bane, Fusion Burst, Glacio Chafe và Electro Flare trên mục tiêu trúng đòn, đồng thời gây 1 lớp Aero Erosion cho mỗi lớp bị loại bỏ.</t>
+          <t>Khi ở trên không, sử dụng &lt;color=Highlight&gt;Resonance Skill Trên Không&lt;/color&gt; sẽ loại bỏ toàn bộ lớp Spectro Frazzle, Havoc Bane, Fusion Burst, Glacio Chafe và Electro Flare trên mục tiêu trúng đòn, đồng thời gây 1 lớp Aero Erosion cho mỗi lớp bị loại bỏ.</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, sử dụng &lt;color=Highlight&gt;enhanced Resonance Skill&lt;/color&gt; để gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt; đầy, sử dụng &lt;color=Highlight&gt;Resonance Skill tăng cường&lt;/color&gt; để gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16143,7 +16143,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và hồi phục HP cho tất cả Resonators trong đội ở gần.</t>
+          <t>Tấn công mục tiêu, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và hồi phục HP cho tất cả Resonator trong đội ở gần.</t>
         </is>
       </c>
     </row>
@@ -16208,7 +16208,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Rover: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Rover: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16273,7 +16273,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Rover: &lt;color=#d4bf5f&gt;Enhanced Heavy Attack&lt;/color&gt;</t>
+          <t>Rover: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Resonance Skill&lt;/color&gt;</t>
+          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Rover: &lt;color=#d4bf5f&gt;Enhanced Resonance Skill&lt;/color&gt;</t>
+          <t>Rover: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và khôi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và khôi phục &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16728,7 +16728,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Kích hoạt kỹ năng để nhảy lên không trung, sau đó &lt;color=Highlight&gt;sử dụng Normal Attack&lt;/color&gt; ngay lập tức để tung ra &lt;color=Highlight&gt;Mid-air Attack cường hóa&lt;/color&gt;, hồi phục HP cho tất cả Resonators trong đội và khôi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Kích hoạt kỹ năng để nhảy lên không trung, sau đó &lt;color=Highlight&gt;dùng Đòn Normal Attack&lt;/color&gt; ngay lập tức để tung ra &lt;color=Highlight&gt;Đòn Mid-air Attack Nâng Cao&lt;/color&gt;, hồi phục HP cho tất cả Resonator trong đội và khôi phục &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16858,7 +16858,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Giữ Normal Attack&lt;/color&gt; ngay sau khi thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt; để nhảy lên không trung, rồi &lt;color=Highlight&gt;sử dụng Normal Attack&lt;/color&gt; ngay sau đó để tung ra &lt;color=Highlight&gt;Mid-air Attack cường hóa&lt;/color&gt;.</t>
+          <t>Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thực hiện &lt;color=Highlight&gt;Giai Đoạn 3 Basic Attack&lt;/color&gt; để nhảy lên không trung, rồi &lt;color=Highlight&gt;dùng Normal Attack&lt;/color&gt; ngay sau đó để tung ra &lt;color=Highlight&gt;Mid-air Attack Được Tăng Cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Khi ở trên không, sử dụng &lt;color=Highlight&gt;Mid-air Resonance Skill&lt;/color&gt; sẽ loại bỏ toàn bộ lớp Spectro Frazzle, Havoc Bane, Fusion Burst, Glacio Chafe và Electro Flare trên mục tiêu trúng đòn, đồng thời gây 1 lớp Aero Erosion cho mỗi lớp bị loại bỏ.</t>
+          <t>Khi ở trên không, sử dụng &lt;color=Highlight&gt;Resonance Skill Trên Không&lt;/color&gt; sẽ loại bỏ toàn bộ lớp Spectro Frazzle, Havoc Bane, Fusion Burst, Glacio Chafe và Electro Flare trên mục tiêu trúng đòn, đồng thời gây 1 lớp Aero Erosion cho mỗi lớp bị loại bỏ.</t>
         </is>
       </c>
     </row>
@@ -16988,7 +16988,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, sử dụng &lt;color=Highlight&gt;enhanced Resonance Skill&lt;/color&gt; để gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt; đầy, sử dụng &lt;color=Highlight&gt;Resonance Skill tăng cường&lt;/color&gt; để gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17053,7 +17053,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Wind&gt;Areo DMG&lt;/color&gt; và hồi phục HP cho tất cả Resonators trong đội ở gần.</t>
+          <t>Tấn công mục tiêu, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và hồi phục HP cho tất cả Resonator trong đội ở gần.</t>
         </is>
       </c>
     </row>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Zani: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Zani: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17183,7 +17183,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Zani: &lt;color=#d4bf5f&gt;Chain Basic Attack&lt;/color&gt;</t>
+          <t>Zani: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack Liên Hoàn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Zani: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Zani: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Zani: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Zani: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Zani: &lt;color=#d4bf5f&gt;Enhanced Resonance Skill&lt;/color&gt;</t>
+          <t>Zani: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17508,7 +17508,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Zani: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt; - Hướng dẫn Heavy Attack Liên Hoàn</t>
+          <t>Zani: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt; - Hướng dẫn Tấn Công Nặng Liên Hoàn</t>
         </is>
       </c>
     </row>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và khôi phục &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và khôi phục &lt;color=Highlight&gt;Đồng Hồ Forte 1&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; đúng thời điểm sau &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Chain Basic Attack&lt;/color&gt;.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; đúng thời điểm sau &lt;color=Highlight&gt;Giai Đoạn 3 Đòn Basic Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Chuỗi Đòn Basic Attack&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. {Cus:Ipt,Touch=Touch PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định để thi triển &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định để thi triển &lt;color=Highlight&gt;Đòn Basic Attack Cấp 3&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. {Cus:Ipt,Touch=Touch PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định để thi triển &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định để thi triển &lt;color=Highlight&gt;Giai Đoạn 3 Đòn Basic Attack&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và chuyển sang tư thế phòng thủ. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong thời gian nhất định để thi triển &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và khiến mục tiêu Trì Trệ.</t>
+          <t>Tấn công mục tiêu gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và chuyển sang tư thế phòng thủ. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; trong thời gian nhất định để thi triển &lt;color=Highlight&gt;Giai Đoạn 3 Đòn Basic Attack&lt;/color&gt;, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và khiến mục tiêu Trì Trệ.</t>
         </is>
       </c>
     </row>
@@ -17898,7 +17898,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Khi Zani không ở &lt;color=Highlight&gt;Inferno Mode&lt;/color&gt; và &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt; đầy, tiêu thụ &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt;, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;Sunburst&lt;/color&gt;.</t>
+          <t>Khi Zani không ở &lt;color=Highlight&gt;Inferno Mode&lt;/color&gt; và &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt; đầy, tiêu thụ &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Kỹ năng Cộng hưởng Nâng cao&lt;/color&gt;, gây &lt;color=Light&gt;DMG Spectro&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;Sunburst&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17963,7 +17963,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Resonance Liberation Stage 1&lt;/color&gt; để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và bước vào &lt;color=Highlight&gt;Inferno Mode&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} liên tục &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tiêu hao &lt;color=Highlight&gt;Forte Gauge 2&lt;/color&gt; và thực hiện các đòn &lt;color=Highlight&gt;Heavy Slashes&lt;/color&gt;. Khi &lt;color=Highlight&gt;Forte Gauge 2&lt;/color&gt; dưới 30 hoặc sau một khoảng thời gian nhất định, Zani có thể kích hoạt &lt;color=Highlight&gt;Resonance Liberation Stage 2&lt;/color&gt;.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Giai Đoạn 1 Resonance Liberation&lt;/color&gt; để gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và bước vào &lt;color=Highlight&gt;Chế Độ Hỏa Ngục&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} liên tục &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; để tiêu hao &lt;color=Highlight&gt;Thanh Forte 2&lt;/color&gt; và thực hiện các đòn &lt;color=Highlight&gt;Chém Nặng&lt;/color&gt;. Khi &lt;color=Highlight&gt;Thanh Forte 2&lt;/color&gt; dưới 30 hoặc sau một khoảng thời gian nhất định, Zani có thể kích hoạt &lt;color=Highlight&gt;Giai Đoạn 2 Resonance Liberation&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18028,7 +18028,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Resonance Liberation Stage 1&lt;/color&gt; để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và bước vào &lt;color=Highlight&gt;Inferno Mode&lt;/color&gt;. Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để tiêu hao &lt;color=Highlight&gt;Forte Gauge 2&lt;/color&gt; và thực hiện các đòn &lt;color=Highlight&gt;Heavy Slash&lt;/color&gt; tích lũy. Khi &lt;color=Highlight&gt;Forte Gauge 2&lt;/color&gt; dưới 30 hoặc sau một khoảng thời gian nhất định, Zani có thể kích hoạt &lt;color=Highlight&gt;Resonance Liberation Stage 2&lt;/color&gt;.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Giai Đoạn 1 Resonance Liberation&lt;/color&gt; để gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và bước vào &lt;color=Highlight&gt;Chế Độ Hỏa Ngục&lt;/color&gt;. Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để tiêu hao &lt;color=Highlight&gt;2 Thanh Forte&lt;/color&gt; và thực hiện các đòn &lt;color=Highlight&gt;Chém Nặng&lt;/color&gt; tích lũy. Khi &lt;color=Highlight&gt;Thanh Forte 2&lt;/color&gt; dưới 30 hoặc sau một khoảng thời gian nhất định, Zani có thể kích hoạt &lt;color=Highlight&gt;Giai Đoạn 2 Resonance Liberation&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Basic Attack Chain</t>
+          <t>Basic Attack Dây Xích</t>
         </is>
       </c>
     </row>
@@ -18158,7 +18158,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Stage 1 Resonance Liberation</t>
+          <t>Giai Đoạn 1 Resonance Liberation</t>
         </is>
       </c>
     </row>
@@ -18223,7 +18223,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Stage 2 Resonance Liberation</t>
+          <t>Giai Đoạn 2 Resonance Liberation</t>
         </is>
       </c>
     </row>
@@ -18288,7 +18288,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Thực hiện gần mục tiêu</t>
+          <t>Kích hoạt gần mục tiêu</t>
         </is>
       </c>
     </row>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Ciaccona: Hướng dẫn &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Ciaccona: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18418,7 +18418,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Ciaccona: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Ciaccona: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Heavy Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Ciaccona: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt; - Chuỗi Mid-air Attack</t>
+          <t>Ciaccona: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt; - Chuỗi Tấn Công Giữa Không</t>
         </is>
       </c>
     </row>
@@ -18548,7 +18548,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Ciaccona: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt; - Chu kỳ Mặt Đất</t>
+          <t>Ciaccona: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt; - Chu kỳ Mặt Đất</t>
         </is>
       </c>
     </row>
@@ -18613,7 +18613,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Ciaccona: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt; - Chu kỳ Giữa Không</t>
+          <t>Ciaccona: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt; - Chu kỳ Giữa Không</t>
         </is>
       </c>
     </row>
@@ -18678,7 +18678,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Ciaccona: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt; - Ngắt Stage 4 Basic Attack</t>
+          <t>Ciaccona: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt; - Ngắt Giai Đoạn 4 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Ciaccona: Hướng dẫn &lt;color=#d4bf5f&gt;Enhanced Heavy Attack&lt;/color&gt;</t>
+          <t>Ciaccona: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Heavy Attack Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18808,7 +18808,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Ciaccona: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Ciaccona: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18873,7 +18873,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Ciaccona: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt; - Thoát Khỏi Resonance Liberation</t>
+          <t>Ciaccona: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt; - Thoát Khỏi Resonance Liberation</t>
         </is>
       </c>
     </row>
@@ -18938,7 +18938,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và khôi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và khôi phục &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để bật lên không trung và tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để bật lên không trung và tấn công mục tiêu, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Thực hiện &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; để nhảy lên không trung, sau đó &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack 3 lần&lt;/color&gt; ngay sau đó để thực hiện Stage 4 Basic Attack.</t>
+          <t>Thực hiện &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; để nhảy lên không trung, sau đó &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Đòn Normal Attack 3 lần&lt;/color&gt; ngay sau đó để thực hiện Giai Đoạn 4 Đòn Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Nhảy lên không trung, rồi &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack 3 lần&lt;/color&gt; để tung chiêu Basic Attack Stage 4.</t>
+          <t>Nhảy lên không trung, rồi &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack 3 lần&lt;/color&gt; để tung chiêu Đòn Cơ Bản Giai Đoạn 4.</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Với 3 đoạn &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;, &lt;color=Highlight&gt;giữ Normal Attack&lt;/color&gt; để thi triển Heavy Attack được tăng cường.</t>
+          <t>Với 3 đoạn &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt;, &lt;color=Highlight&gt;giữ Đòn Normal Attack&lt;/color&gt; để thi triển Đòn Heavy Attack được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -19458,7 +19458,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Resonance Liberation, Ciaccona sẽ bất động trong một khoảng thời gian ngắn. {Cus:Ipt,Touch=Touch PC=press Gamepad=press} nút đúng lúc theo chỉ dẫn để tạo ra &lt;color=Highlight&gt;Symphonic Poem: Tonic&lt;/color&gt;, tấn công các mục tiêu xung quanh.</t>
+          <t>Sau khi sử dụng Resonance Liberation, Ciaccona sẽ bất động trong một khoảng thời gian ngắn. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút đúng lúc theo chỉ dẫn để tạo ra &lt;color=Highlight&gt;Thơ Giao Hưởng: Chủ Âm&lt;/color&gt;, tấn công các mục tiêu xung quanh.</t>
         </is>
       </c>
     </row>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Cartethyia: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Cartethyia: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Cartethyia: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Cartethyia: &lt;color=#d4bf5f&gt;Hướng dẫn Đòn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Cartethyia: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Cartethyia: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Cartethyia: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Cartethyia: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Fleurdelys: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Fleurdelys: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Fleurdelys: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Fleurdelys: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19978,7 +19978,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Fleurdelys: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Fleurdelys: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20044,8 +20044,8 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Cartethyia thực hiện 4 giai đoạn Basic Attack, sau đó triệu hồi &lt;color=Highlight&gt;Kiếm of Divinity's Shadow&lt;/color&gt; theo đòn tấn công cuối. 
-Khi thi triển Đòn Lao Xuống, cô sẽ thu hồi &lt;color=Highlight&gt;Kiếm of Divinity's Shadow&lt;/color&gt;.</t>
+          <t>Cartethyia thực hiện 4 giai đoạn Basic Attack, sau đó triệu hồi &lt;color=Highlight&gt;Thanh Kiếm Bóng Tối Thần Tính&lt;/color&gt; theo đòn tấn công cuối. 
+Khi thi triển Đòn Lao Xuống, cô sẽ thu hồi &lt;color=Highlight&gt;Thanh Kiếm Bóng Tối Thần Tính&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20111,8 +20111,8 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Khi sử dụng Cartethyia, giữ Normal Attack để gây Aero DMG và kéo mục tiêu về phía trước, sau đó triệu hồi &lt;color=Highlight&gt;Kiếm of Discord's Shadow&lt;/color&gt;.
-Mid-air Attack sẽ thu hồi &lt;color=Highlight&gt;Kiếm of Discord's Shadow&lt;/color&gt;.</t>
+          <t>Khi sử dụng Cartethyia, giữ Normal Attack để gây Sát Thương Aero và kéo mục tiêu về phía trước, sau đó triệu hồi &lt;color=Highlight&gt;Bóng Kiếm của Discord&lt;/color&gt;.
+Tấn Công Giữa Không Trung sẽ thu hồi &lt;color=Highlight&gt;Bóng Kiếm của Discord&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20178,8 +20178,8 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Cartethyia sử dụng Resonance Skill gây Aero DMG và triệu hồi &lt;color=Highlight&gt;Kiếm of Virtue's Shadow&lt;/color&gt;.
-Mid-air Attack sẽ thu hồi &lt;color=Highlight&gt;Kiếm of Virtue's Shadow&lt;/color&gt;.</t>
+          <t>Cartethyia sử dụng Resonance Skill gây Sát Thương Aero và triệu hồi &lt;color=Highlight&gt;Kiếm Bóng Ma Đức Hạnh&lt;/color&gt;.
+Tấn Công Giữa Không Trung sẽ thu hồi &lt;color=Highlight&gt;Kiếm Bóng Ma Đức Hạnh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20246,9 +20246,9 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill, Heavy Attack hoặc giai đoạn cuối của Basic Attack sẽ triệu hồi các &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; khác nhau.
-Thực hiện Đòn Mid-air Attack với &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; trên chiến trường sẽ thu hồi &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; và kích hoạt &lt;color=Highlight&gt;Heart of Virtue&lt;/color&gt;, &lt;color=Highlight&gt;Mandate of Divinity&lt;/color&gt; và &lt;color=Highlight&gt;Power of Discord&lt;/color&gt; tương ứng.
-Fleurdelys nhận được nhiều hiệu ứng tăng cường khác nhau khi thu hồi &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt;.</t>
+          <t>Kích hoạt Resonance Skill, Đòn Heavy Attack hoặc giai đoạn cuối của Đòn Basic Attack sẽ triệu hồi các &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; khác nhau.
+Thực hiện Đòn Tấn Công Giữa Không với &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; trên chiến trường sẽ thu hồi &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; và kích hoạt &lt;color=Highlight&gt;Trái Tim Nhân Đức&lt;/color&gt;, &lt;color=Highlight&gt;Thiên Mệnh Thần Quyền&lt;/color&gt; và &lt;color=Highlight&gt;Sức Mạnh Tacet Discord&lt;/color&gt; tương ứng.
+Fleurdelys nhận được nhiều hiệu ứng tăng cường khác nhau khi thu hồi &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20314,8 +20314,8 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Cartethyia biến hình thành Fleurdelys bằng cách kích hoạt Resonance Liberation và bước vào trạng thái &lt;color=Highlight&gt;Manifest&lt;/color&gt;.
-&lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; mang lại cho Fleurdelys những thưởng thức bổ sung.</t>
+          <t>Cartethyia biến hình thành Fleurdelys bằng cách kích hoạt Resonance Liberation và bước vào trạng thái &lt;color=Highlight&gt;Hiện Thân&lt;/color&gt;.
+&lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; mang lại cho Fleurdelys những thưởng thức bổ sung.</t>
         </is>
       </c>
     </row>
@@ -20383,10 +20383,10 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Fleurdelys thực hiện 5 giai đoạn Basic Attack gây Aero DMG và hồi phục &lt;color=Highlight&gt;Conviction&lt;/color&gt;.
-Giai đoạn 5 của Basic Attack ngay lập tức kích hoạt &lt;color=Wind&gt;Aero Erosion&lt;/color&gt; một lần và tiêu hao 1 tầng &lt;color=Wind&gt;Aero Erosion&lt;/color&gt;.
-Khi có &lt;color=Highlight&gt;Heart of Virtue&lt;/color&gt;, tăng khả năng kháng gián đoạn, và giai đoạn 4 của Basic Attack sẽ triệu hồi một lá chắn làm Trì Hoãn kẻ địch.
-Khi có &lt;color=Highlight&gt;Power of Discord&lt;/color&gt;, giai đoạn 5 của Basic Attack sẽ lan truyền số tầng &lt;color=Wind&gt;Aero Erosion&lt;/color&gt; cao nhất trong số các mục tiêu.</t>
+          <t>Fleurdelys thực hiện 5 giai đoạn Basic Attack gây Sát Thương Aero và hồi phục &lt;color=Highlight&gt;Điểm Niềm Tin&lt;/color&gt;.
+Giai đoạn 5 của Basic Attack ngay lập tức kích hoạt &lt;color=Wind&gt;Sát Thương Aero Erosion&lt;/color&gt; một lần và tiêu hao 1 tầng &lt;color=Wind&gt;Aero Erosion&lt;/color&gt;.
+Khi có &lt;color=Highlight&gt;Trái Tim Nhân Đức&lt;/color&gt;, tăng khả năng kháng gián đoạn, và giai đoạn 4 của Basic Attack sẽ triệu hồi một lá chắn làm Trì Hoãn kẻ địch.
+Khi có &lt;color=Highlight&gt;Sức Mạnh Tacet Discord&lt;/color&gt;, giai đoạn 5 của Basic Attack sẽ lan truyền số tầng &lt;color=Wind&gt;Aero Erosion&lt;/color&gt; cao nhất trong số các mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -20454,9 +20454,9 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Với tư cách là Fleurdelys, hãy sử dụng Kỹ Năng Nhảy trên mặt đất để khóa mục tiêu và thực hiện Đòn Chém Lên. Khi ở trên không, thực hiện tối đa 3 giai đoạn Mid-air Attack để gây Aero DMG và hồi phục &lt;color=Highlight&gt;Conviction&lt;/color&gt;. Giai đoạn 3 của Mid-air Attack sẽ ngay lập tức kích hoạt Sát Thương &lt;color=Wind&gt;Aero Erosion&lt;/color&gt; một lần và tiêu hao 1 tầng &lt;color=Wind&gt;Aero Erosion&lt;/color&gt;.
-Với &lt;color=Highlight&gt;Heart of Virtue&lt;/color&gt;, tăng khả năng kháng cự gián đoạn.
-Với &lt;color=Highlight&gt;Power of Discord&lt;/color&gt;, giai đoạn 2 của Mid-air Attack sẽ lan truyền số tầng &lt;color=Wind&gt;Aero Erosion&lt;/color&gt; cao nhất trong số các mục tiêu.</t>
+          <t>Với tư cách là Fleurdelys, hãy sử dụng Kỹ Năng Nhảy trên mặt đất để khóa mục tiêu và thực hiện Đòn Chém Lên. Khi ở trên không, thực hiện tối đa 3 giai đoạn Mid-air Attack để gây Sát Thương Aero và hồi phục &lt;color=Highlight&gt;Niềm Tin&lt;/color&gt;. Giai đoạn 3 của Mid-air Attack sẽ ngay lập tức kích hoạt Sát Thương &lt;color=Wind&gt;Xói Mòn Aero&lt;/color&gt; một lần và tiêu hao 1 tầng &lt;color=Wind&gt;Xói Mòn Aero&lt;/color&gt;.
+Với &lt;color=Highlight&gt;Trái Tim Đức Hạnh&lt;/color&gt;, tăng khả năng kháng cự gián đoạn.
+Với &lt;color=Highlight&gt;Sức Mạnh Discord&lt;/color&gt;, giai đoạn 2 của Mid-air Attack sẽ lan truyền số tầng &lt;color=Wind&gt;Xói Mòn Aero&lt;/color&gt; cao nhất trong số các mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -20523,9 +20523,9 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Resonance Skill của Fleurdelys có hai giai đoạn. Mỗi giai đoạn gây Aero DMG và hồi phục &lt;color=Highlight&gt;Conviction&lt;/color&gt;.
-Giai đoạn hai của Resonance Skill ngay lập tức kích hoạt &lt;color=Wind&gt;Aero Erosion&lt;/color&gt; lên mục tiêu, sau đó tiêu hao 1 tầng &lt;color=Wind&gt;Aero Erosion&lt;/color&gt;.
-Khi có &lt;color=Highlight&gt;Power of Discord&lt;/color&gt;, giai đoạn hai của Resonance Skill sẽ lan truyền số tầng &lt;color=Wind&gt;Aero Erosion&lt;/color&gt; cao nhất trong số các mục tiêu.</t>
+          <t>Resonance Skill của Fleurdelys có hai giai đoạn. Mỗi giai đoạn gây Sát Thương Aero và hồi phục &lt;color=Highlight&gt;Điểm Niềm Tin&lt;/color&gt;.
+Giai đoạn hai của Resonance Skill ngay lập tức kích hoạt &lt;color=Wind&gt;Sát Thương Aero Erosion&lt;/color&gt; lên mục tiêu, sau đó tiêu hao 1 tầng &lt;color=Wind&gt;Aero Erosion&lt;/color&gt;.
+Khi có &lt;color=Highlight&gt;Sức Mạnh Tacet Discord&lt;/color&gt;, giai đoạn hai của Resonance Skill sẽ lan truyền số tầng &lt;color=Wind&gt;Aero Erosion&lt;/color&gt; cao nhất trong số các mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -20592,9 +20592,9 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Với tư cách là Fleurdelys, giữ Normal Attack để lao về phía trước, gây Aero DMG và hồi phục &lt;color=Highlight&gt;Conviction&lt;/color&gt;.
-Sử dụng Basic Attack trong trạng thái này để lùi lại và gây Aero DMG lên mục tiêu phía trước, đồng thời hồi phục &lt;color=Highlight&gt;Conviction&lt;/color&gt;.
-Với &lt;color=Highlight&gt;Power of Discord&lt;/color&gt;, Heavy Attack được tăng cường sẽ lan truyền số tầng &lt;color=Wind&gt;Aero Erosion&lt;/color&gt; cao nhất từ mục tiêu.</t>
+          <t>Với tư cách là Fleurdelys, giữ Đòn Normal Attack để lao về phía trước, gây Sát Thương Aero và hồi phục &lt;color=Highlight&gt;Niềm Tin&lt;/color&gt;.
+Sử dụng Đòn Cơ Bản trong trạng thái này để lùi lại và gây Sát Thương Aero lên mục tiêu phía trước, đồng thời hồi phục &lt;color=Highlight&gt;Niềm Tin&lt;/color&gt;.
+Với &lt;color=Highlight&gt;Sức Mạnh Tacet Discord&lt;/color&gt;, Đòn Nặng được tăng cường sẽ lan truyền số tầng &lt;color=Wind&gt;Xói Mòn Aero&lt;/color&gt; cao nhất từ mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -20660,8 +20660,8 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Các đòn tấn công của Fleurdelys hồi phục &lt;color=Highlight&gt;Conviction&lt;/color&gt; khi trúng đích.
-Khi &lt;color=Highlight&gt;Conviction&lt;/color&gt; đạt 120 điểm, hãy sử dụng Resonance Liberation để Fleurdelys thi triển &lt;color=Highlight&gt;Blade of Howling Squall&lt;/color&gt;.</t>
+          <t>Các đòn tấn công của Fleurdelys hồi phục &lt;color=Highlight&gt;Điểm Niềm Tin&lt;/color&gt; khi trúng đích.
+Khi &lt;color=Highlight&gt;Điểm Niềm Tin&lt;/color&gt; đạt 120 điểm, hãy sử dụng Resonance Liberation để Fleurdelys thi triển &lt;color=Highlight&gt;Lưỡi Kiếm Gió Hú&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack 1&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20791,7 +20791,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack 2&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20921,7 +20921,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20986,7 +20986,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Resonance Skill Chain Attack&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Chuỗi Resonance Skill - Phần 1&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21051,7 +21051,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Resonance Skill Chain Attack&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Chuỗi Resonance Skill - Phần 2&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21116,7 +21116,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Enhanced Heavy Attack 1&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Nâng Cao 1&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21181,7 +21181,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Enhanced Heavy Attack 2&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Nâng Cao 2&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Resonance Skill Finisher&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Hoàn Thành&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Lupa: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Lupa: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21376,7 +21376,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi &lt;color=Highlight&gt;Đồng Hồ Forte 1&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Ấn PC=press Gamepad=press} Normal Attack đúng lúc sau Stage 3 Basic Attack để tung &lt;color=Highlight&gt;Mid-air Attack Stage 1&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt;.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Đòn Thường đúng lúc sau Giai Đoạn 3 Đòn Cơ Bản để tung &lt;color=Highlight&gt;Giai Đoạn 1 Đòn Trên Không&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21506,7 +21506,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 3 đòn Mid-air Attack tại chi phí STA, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 3 đòn Tấn Công Giữa Không tại chi phí STA, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi &lt;color=Highlight&gt;Đồng Vọng Cường Độ 1&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21571,7 +21571,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Giữ Normal Attack giữa không trung để thực hiện Đòn Lao Xuống, tiêu hao STA và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Trong một khoảng thời gian sau khi tung &lt;color=Highlight&gt;Plunging Attack&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để thực hiện &lt;color=Highlight&gt;Plunging Chain Attack&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt;.</t>
+          <t>Giữ Normal Attack giữa không trung để thực hiện Đòn Lao Xuống, tiêu hao STA và gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;. Trong một khoảng thời gian sau khi tung &lt;color=Highlight&gt;Đòn Lao Xuống&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để thực hiện &lt;color=Highlight&gt;Đòn Lao Xuống Liên Hoàn&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;1 Thanh Forte&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21636,7 +21636,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu bằng STA, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Tấn công mục tiêu bằng STA, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi &lt;color=Highlight&gt;Đồng Vị Khu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Sử dụng Resonance Skill để gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và &lt;color=Highlight&gt;mark&lt;/color&gt; mục tiêu. Sau khi dùng Resonance Skill, &lt;color=Highlight&gt;Chain Resonance Skill&lt;/color&gt; sẽ khả dụng trong một khoảng thời gian.</t>
+          <t>Sử dụng Resonance Skill để gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và &lt;color=Highlight&gt;đánh dấu&lt;/color&gt; mục tiêu. Sau khi dùng Resonance Skill, &lt;color=Highlight&gt;Resonance Skill Liên Hoàn&lt;/color&gt; sẽ khả dụng trong một khoảng thời gian.</t>
         </is>
       </c>
     </row>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Ngay sau khi dùng Resonance Skill, sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.</t>
+          <t>Ngay sau khi dùng Resonance Skill, sử dụng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Giai Đoạn 2 Đòn Basic Attack&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21831,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Giữ Resonance Skill để nhảy lên không trung và {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong thời gian nhất định để tung ra &lt;color=Highlight&gt;Mid-air Attack Stage 1&lt;/color&gt;.</t>
+          <t>Giữ Resonance Skill để nhảy lên không trung và {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong thời gian nhất định để tung ra &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không Trọng 1&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Khi có ít nhất một nửa &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt;, giữ Đòn Attack 1 Thường để sử dụng &lt;color=Highlight&gt;Enhanced Heavy Attack 1&lt;/color&gt;, tấn công mục tiêu tiêu tốn STA, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi 1 điểm &lt;color=Highlight&gt;Forte Gauge 2&lt;/color&gt;.</t>
+          <t>Khi có ít nhất một nửa &lt;color=Highlight&gt;Đồng Hồ Forte 1&lt;/color&gt;, giữ Đòn Normal Attack để sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack Nâng Cao 1&lt;/color&gt;, tấn công mục tiêu tiêu tốn STA, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi 1 điểm &lt;color=Highlight&gt;Đồng Hồ Forte 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21961,7 +21961,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Khi có ít nhất một nửa &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt; và 1 điểm &lt;color=Highlight&gt;Forte Gauge 2&lt;/color&gt;, giữ Normal Attack để sử dụng &lt;color=Highlight&gt;Enhanced Heavy Attack 2&lt;/color&gt;, tấn công mục tiêu tiêu tốn STA, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi 1 điểm &lt;color=Highlight&gt;Forte Gauge 2&lt;/color&gt;.</t>
+          <t>Khi có ít nhất một nửa &lt;color=Highlight&gt;Đồng Hồ Forte 1&lt;/color&gt; và 1 điểm &lt;color=Highlight&gt;Đồng Hồ Forte 2&lt;/color&gt;, giữ Đòn Normal Attack để sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack Nâng Cao 2&lt;/color&gt;, tấn công mục tiêu tiêu tốn STA, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi 1 điểm &lt;color=Highlight&gt;Đồng Hồ Forte 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -22026,7 +22026,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Khi có ít nhất một nửa &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt;, &lt;color=Highlight&gt;Mid-air Attack Stage 3&lt;/color&gt; sẽ trở thành &lt;color=Highlight&gt;Enhanced Mid-air Attack&lt;/color&gt;: tấn công mục tiêu tiêu tốn STA, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi 1 điểm &lt;color=Highlight&gt;Forte Gauge 2&lt;/color&gt;.</t>
+          <t>Khi có ít nhất một nửa &lt;color=Highlight&gt;Đồng Hồ Forte 1&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không Giai Đoạn 3&lt;/color&gt; sẽ trở thành &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không Nâng Cao&lt;/color&gt;: tấn công mục tiêu tiêu tốn STA, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi 1 điểm &lt;color=Highlight&gt;Đồng Hồ Forte 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -22091,7 +22091,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge 2&lt;/color&gt; đầy, có thể kích hoạt Kết Thúc Resonance Skill, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và phục hồi &lt;color=Highlight&gt;Concerto Energy&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Đồng Hồ Forte 2&lt;/color&gt; đầy, có thể kích hoạt Kết Thúc Resonance Skill, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và phục hồi &lt;color=Highlight&gt;Concerto Energy&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -22156,7 +22156,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Resonance Liberation, Lupa có thể nhanh chóng hồi phục &lt;color=Highlight&gt;Forte Gauge 1&lt;/color&gt; thông qua Đòn Attack 1 Thường, và hồi phục &lt;color=Highlight&gt;Forte Gauge 2&lt;/color&gt; bằng cách sử dụng &lt;color=Highlight&gt;Enhanced Mid-air Attack&lt;/color&gt;, &lt;color=Highlight&gt;Enhanced Heavy Attack 1&lt;/color&gt; hoặc &lt;color=Highlight&gt;Enhanced Heavy Attack 2&lt;/color&gt;. Sau đó, cô có thể sử dụng Resonance Skill Hoàn Tất để gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Concerto Energy&lt;/color&gt;.</t>
+          <t>Sau khi sử dụng Resonance Liberation, Lupa có thể nhanh chóng hồi phục &lt;color=Highlight&gt;Đồng Hồ Forte 1&lt;/color&gt; thông qua Đòn Normal Attack, và hồi phục &lt;color=Highlight&gt;Đồng Hồ Forte 2&lt;/color&gt; bằng cách sử dụng &lt;color=Highlight&gt;Đòn Tấn Công Nâng Cao Giữa Không Trung&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Heavy Attack Nâng Cao 1&lt;/color&gt; hoặc &lt;color=Highlight&gt;Đòn Heavy Attack Nâng Cao 2&lt;/color&gt;. Sau đó, cô có thể sử dụng Resonance Skill Hoàn Tất để gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Concerto Energy&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -22221,7 +22221,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Heavy Attack Cường Hóa</t>
+          <t>Đòn Heavy Attack Cường Hóa</t>
         </is>
       </c>
     </row>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Kỹ Năng Enhanced Resonance</t>
+          <t>Resonance Skill Cường Hóa</t>
         </is>
       </c>
     </row>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Heavy Attack Cường Hóa</t>
+          <t>Đòn Heavy Attack Cường Hóa</t>
         </is>
       </c>
     </row>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Phrolova: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt; 1</t>
+          <t>Phrolova: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt; 1</t>
         </is>
       </c>
     </row>
@@ -22546,7 +22546,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Phrolova: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt; 1</t>
+          <t>Phrolova: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt; 1</t>
         </is>
       </c>
     </row>
@@ -22611,7 +22611,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Phrolova: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt; 2</t>
+          <t>Phrolova: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt; 2</t>
         </is>
       </c>
     </row>
@@ -22676,7 +22676,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Phrolova: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt; 2</t>
+          <t>Phrolova: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt; 2</t>
         </is>
       </c>
     </row>
@@ -22741,7 +22741,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Phrolova: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Phrolova: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22806,7 +22806,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Phrolova: &lt;color=#d4bf5f&gt;Forte Gauge&lt;/color&gt; 1</t>
+          <t>Phrolova: &lt;color=#d4bf5f&gt;Hướng dẫn Đồng Hồ Forte&lt;/color&gt; 1</t>
         </is>
       </c>
     </row>
@@ -22871,7 +22871,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Phrolova: &lt;color=#d4bf5f&gt;Forte Gauge&lt;/color&gt; 2</t>
+          <t>Phrolova: &lt;color=#d4bf5f&gt;Hướng dẫn Đồng Hồ Forte&lt;/color&gt; 2</t>
         </is>
       </c>
     </row>
@@ -22936,7 +22936,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Phrolova: &lt;color=#d4bf5f&gt;Forte Gauge&lt;/color&gt; 3</t>
+          <t>Phrolova: &lt;color=#d4bf5f&gt;Hướng dẫn Đồng Hồ Forte&lt;/color&gt; 3</t>
         </is>
       </c>
     </row>
@@ -23001,7 +23001,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Phrolova: &lt;color=#d4bf5f&gt;Enhanced Heavy Attack&lt;/color&gt;</t>
+          <t>Phrolova: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23066,7 +23066,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Phrolova: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt; 1</t>
+          <t>Phrolova: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt; 1</t>
         </is>
       </c>
     </row>
@@ -23131,7 +23131,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Phrolova: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt; 2</t>
+          <t>Phrolova: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt; 2</t>
         </is>
       </c>
     </row>
@@ -23196,7 +23196,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt; sẽ giảm &lt;color=Highlight&gt;Forte Gauge - Red&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. &lt;color=Highlight&gt;Giai Đoạn 3 Đòn Basic Attack&lt;/color&gt; sẽ giảm &lt;color=Highlight&gt;Đồng Hồ Forte - Đỏ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23261,7 +23261,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. Cấp &lt;color=Highlight&gt;Forte Gauge - Purple&lt;/color&gt;.</t>
+          <t>Tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. Cấp &lt;color=Highlight&gt;Forte Gauge - Màu Tím&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23326,7 +23326,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; sau &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt;.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; sau &lt;color=Highlight&gt;Giai Đoạn 3 Đòn Basic Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Resonance Skill Cường Hóa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23391,7 +23391,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Thực hiện &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sau &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để kích hoạt &lt;color=Highlight&gt;Enhanced Basic Attack&lt;/color&gt;.</t>
+          <t>Thực hiện &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; sau &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để kích hoạt &lt;color=Highlight&gt;Đòn Basic Attack Nâng Cao&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23456,7 +23456,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tấn công, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tấn công, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23586,7 +23586,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Khi kích hoạt &lt;color=Highlight&gt;Inherent Skill - Accidental&lt;/color&gt;, &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Echo Skill&lt;/color&gt;, thanh &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; tiếp theo nhận được sẽ chuyển thành &lt;color=Highlight&gt;Forte Gauge - Combined&lt;/color&gt;.</t>
+          <t>Khi kích hoạt &lt;color=Highlight&gt;Kỹ Năng Nội Tại - Ngẫu Nhiên&lt;/color&gt;, &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; hoặc &lt;color=Highlight&gt;Kỹ Năng Vọng Âm&lt;/color&gt;, thanh &lt;color=Highlight&gt;Đồng Vận Lượng&lt;/color&gt; tiếp theo nhận được sẽ chuyển thành &lt;color=Highlight&gt;Đồng Vận Lượng - Hợp Nhất&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23651,7 +23651,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Khi kích hoạt &lt;color=Highlight&gt;Inherent Skill - Accidental&lt;/color&gt;, &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Echo Skill&lt;/color&gt;, thanh &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; tiếp theo nhận được sẽ chuyển thành &lt;color=Highlight&gt;Forte Gauge - Combined&lt;/color&gt;.</t>
+          <t>Khi kích hoạt &lt;color=Highlight&gt;Kỹ Năng Nội Tại - Ngẫu Nhiên&lt;/color&gt;, &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; hoặc &lt;color=Highlight&gt;Kỹ Năng Vọng Âm&lt;/color&gt;, thanh &lt;color=Highlight&gt;Đồng Vận Lượng&lt;/color&gt; tiếp theo nhận được sẽ chuyển thành &lt;color=Highlight&gt;Đồng Vận Lượng - Hợp Nhất&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23716,7 +23716,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; mới sẽ đẩy toàn bộ &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; sang trái và loại bỏ &lt;color=Highlight&gt;Forte Gauge - Red&lt;/color&gt; hoặc &lt;color=Highlight&gt;Forte Gauge - Purple&lt;/color&gt; ngoài cùng bên trái.</t>
+          <t>Khi &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt; đầy, &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt; mới sẽ đẩy toàn bộ &lt;color=Highlight&gt;Thanh Forte&lt;/color&gt; sang trái và loại bỏ &lt;color=Highlight&gt;Thanh Forte - Đỏ&lt;/color&gt; hoặc &lt;color=Highlight&gt;Thanh Forte - Tím&lt;/color&gt; ngoài cùng bên trái.</t>
         </is>
       </c>
     </row>
@@ -23781,7 +23781,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, có thể sử dụng &lt;color=Highlight&gt;Enhanced Heavy Attack&lt;/color&gt;, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và mở khóa &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt; đầy, có thể sử dụng &lt;color=Highlight&gt;Đòn Nặng Tăng Cường&lt;/color&gt;, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; và mở khóa &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23849,10 +23849,10 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ mở khóa &lt;color=Highlight&gt;Enhanced State&lt;/color&gt;, trong đó Phrolova sẽ đưa ra các tín hiệu sau.
-- &lt;color=Highlight&gt;Cue - Basic Attack&lt;/color&gt;: {Cus:Ipt,Touch=tap PC=press Gamepad=press} Kỹ Năng Thường.
-- &lt;color=Highlight&gt;Cue - Dodge&lt;/color&gt;: {Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge.
-- &lt;color=Highlight&gt;Cue - Curtain Call&lt;/color&gt;: {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Liberation.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ mở khóa &lt;color=Highlight&gt;Trạng Thái Tăng Cường&lt;/color&gt;, trong đó Phrolova sẽ đưa ra các tín hiệu sau.
+- &lt;color=Highlight&gt;Tín Hiệu - Kỹ Năng Cơ Bản&lt;/color&gt;: {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} Kỹ Năng Thường.
+- &lt;color=Highlight&gt;Tín Hiệu - Né Tránh&lt;/color&gt;: {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} Né Tránh.
+- &lt;color=Highlight&gt;Tín Hiệu - Hồi Kết&lt;/color&gt;: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -23918,8 +23918,8 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Enhanced State&lt;/color&gt;, chuyển sang Resonators khác sẽ khiến Hecate tự động thi triển &lt;color=Highlight&gt;Basic Attack - Hecate&lt;/color&gt; tấn công mục tiêu.
-Chuyển về Phrolova sẽ kết thúc trạng thái &lt;color=Highlight&gt;Enhanced State&lt;/color&gt;.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Tăng Cường&lt;/color&gt;, chuyển sang Resonator khác sẽ khiến Hecate tự động thi triển &lt;color=Highlight&gt;Đòn Basic Attack - Hecate&lt;/color&gt; tấn công mục tiêu.
+Chuyển về Phrolova sẽ kết thúc trạng thái &lt;color=Highlight&gt;Tăng Cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24049,7 +24049,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Kỹ Năng Enhanced Resonance Sẵn Sàng</t>
+          <t>Resonance Skill Cường Hóa Sẵn Sàng</t>
         </is>
       </c>
     </row>
@@ -24179,7 +24179,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Iuno: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Iuno: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24244,7 +24244,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp bằng &lt;color=Highlight&gt;Moonring&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp bằng &lt;color=Highlight&gt;Vòng Trăng&lt;/color&gt;, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Iuno: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Iuno: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24439,7 +24439,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Giữ Normal Attack để tự động thực hiện 3 Basic Attack, gây Aero DMG.</t>
+          <t>Giữ Normal Attack để tự động thực hiện 3 Đòn Basic Attack, gây Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -24504,7 +24504,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Iuno: &lt;color=#d4bf5f&gt;Resonance Skill - Pulse of Origins&lt;/color&gt;</t>
+          <t>Iuno: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ năng Cộng Hưởng - Nhịp Đập Khởi Nguyên&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Lao về phía trước, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Lao về phía trước, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24637,8 +24637,8 @@
       <c r="M371" t="inlineStr">
         <is>
           <t>Sau khi sử dụng một số kỹ năng nhất định, Resonance Skill của Iuno sẽ được thay thế bằng Khúc Kết trong 5 giây.
-Sử dụng Khúc Kết sẽ tung ra hàng loạt đòn tấn công, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và kích hoạt trạng thái &lt;color=Highlight&gt;Lunar Cycle&lt;/color&gt;.
-Iuno mặc định sẽ bước vào &lt;color=Highlight&gt;Lunar Cycle - Half Moon&lt;/color&gt;, trong đó cô tấn công bằng &lt;color=Highlight&gt;Moonring&lt;/color&gt; để hồi phục Thanh Forte.</t>
+Sử dụng Khúc Kết sẽ tung ra hàng loạt đòn tấn công, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và kích hoạt trạng thái &lt;color=Highlight&gt;Chu Kỳ Mặt Trăng&lt;/color&gt;.
+Iuno mặc định sẽ bước vào &lt;color=Highlight&gt;Chu Kỳ Mặt Trăng - Trăng Khuyết&lt;/color&gt;, trong đó cô tấn công bằng &lt;color=Highlight&gt;Vòng Trăng&lt;/color&gt; để hồi phục Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -24707,7 +24707,7 @@
         <is>
           <t>Sau khi kích hoạt &lt;color=Highlight&gt;Lunar Cycle&lt;/color&gt; với Closing Refrain, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy để tung đòn &lt;color=Highlight&gt;Heavy Attack - Flux&lt;/color&gt; và chuyển sang &lt;color=Highlight&gt;Lunar Cycle - New Moon&lt;/color&gt;.
 Trong trạng thái này, Iuno tấn công bằng &lt;color=Highlight&gt;Moonbow&lt;/color&gt; với chi phí Forte Gauge, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy thêm lần nữa để chuyển về &lt;color=Highlight&gt;Lunar Cycle - Half Moon&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Nhảy thêm lần nữa để chuyển về &lt;color=Highlight&gt;Lunar Cycle - Half Moon&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24772,7 +24772,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Iuno: &lt;color=#d4bf5f&gt;Resonance Skill - Arc Beyond the Edge&lt;/color&gt;</t>
+          <t>Iuno: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ năng Cộng Hưởng - Vòng Cung Vượt Biên&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Khi Iuno ở trạng thái &lt;color=Highlight&gt;Lunar Cycle - New Moon&lt;/color&gt;, Resonance Skill của cô sẽ được thay thế bằng &lt;color=Highlight&gt;Arc Beyond the Edge&lt;/color&gt;, với 2 lượt sử dụng ban đầu.</t>
+          <t>Khi Iuno ở trạng thái &lt;color=Highlight&gt;Chu Kỳ Mặt Trăng - Trăng Non&lt;/color&gt;, Resonance Skill của cô sẽ được thay thế bằng &lt;color=Highlight&gt;Vòng Cung Vượt Giới&lt;/color&gt;, với 2 lượt sử dụng ban đầu.</t>
         </is>
       </c>
     </row>
@@ -24903,8 +24903,8 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Iuno có thể chuyển đổi giữa trạng thái &lt;color=Highlight&gt;Half Moon&lt;/color&gt; và &lt;color=Highlight&gt;New Moon&lt;/color&gt;. Mặc định, Iuno sẽ vào trạng thái &lt;color=Highlight&gt;Half Moon&lt;/color&gt; trước.
-Kỹ năng Nhảy của Iuno được thay thế bằng &lt;color=Highlight&gt;Heavy Attack - Flux&lt;/color&gt;, có thể kích hoạt để chuyển đổi trạng thái.</t>
+          <t>Iuno có thể chuyển đổi giữa trạng thái &lt;color=Highlight&gt;Trăng Khuyết&lt;/color&gt; và &lt;color=Highlight&gt;Trăng Non&lt;/color&gt;. Mặc định, Iuno sẽ vào trạng thái &lt;color=Highlight&gt;Trăng Khuyết&lt;/color&gt; trước.
+Kỹ năng Nhảy của Iuno được thay thế bằng &lt;color=Highlight&gt;Heavy Attack - Luồng Chảy&lt;/color&gt;, có thể kích hoạt để chuyển đổi trạng thái.</t>
         </is>
       </c>
     </row>
@@ -24969,7 +24969,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Iuno: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Iuno: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25034,7 +25034,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và kích hoạt trực tiếp &lt;color=Highlight&gt;Lunar Cycle&lt;/color&gt;.</t>
+          <t>Gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và kích hoạt trực tiếp &lt;color=Highlight&gt;Lunar Cycle&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25099,7 +25099,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Iuno: &lt;color=#d4bf5f&gt;Heavy Attack - Absolute Fullness&lt;/color&gt;</t>
+          <t>Iuno: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh - Tuyệt Đối Viên Mãn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25165,8 +25165,8 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy của Iuno đạt tối đa, Heavy Attack của cô sẽ được thay thế bằng &lt;color=Highlight&gt;Absolute Fullness&lt;/color&gt;.
-Sử dụng Tròn Full Tuyệt Đối sẽ gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; lên kẻ địch xung quanh (được tính là Sát Thương Resonance Liberation) và hồi phục HP cho Resonators trong đội.</t>
+          <t>Khi Concerto Energy của Iuno đạt tối đa, Đòn Heavy Attack của cô sẽ được thay thế bằng &lt;color=Highlight&gt;Tròn Đầy Tuyệt Đối&lt;/color&gt;.
+Sử dụng Tròn Đầy Tuyệt Đối sẽ gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; lên kẻ địch xung quanh (được tính là Sát Thương Resonance Liberation) và hồi phục HP cho các Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -25296,7 +25296,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Augusta: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Augusta: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25426,7 +25426,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tung đòn Heavy Attack, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tung đòn Heavy Attack, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25491,7 +25491,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Augusta: &lt;color=#d4bf5f&gt;Chain Heavy Attack&lt;/color&gt;</t>
+          <t>Augusta: &lt;color=#d4bf5f&gt;Hướng dẫn Kết Hợp Heavy Attack (I)&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25556,7 +25556,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Prowess&lt;/color&gt; đạt tối đa, &lt;color=Highlight&gt;Heavy Attack - Steelclash&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Backstep&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và tiêu hao toàn bộ Uy Lực. Trong hành động, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Spinslash&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Uy Lực&lt;/color&gt; đạt tối đa, &lt;color=Highlight&gt;Đòn Heavy Attack - Va Đập Thép&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Đòn Heavy Attack - Hồi Sấm: Lùi Bước&lt;/color&gt;, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; và tiêu hao toàn bộ Uy Lực. Trong hành động, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Đòn Normal Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Đòn Heavy Attack - Hồi Sấm: Xoay Đòn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25621,7 +25621,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống trên không, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống trên không, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25686,7 +25686,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Augusta: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Augusta: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25751,7 +25751,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Augusta nhảy lên rồi đập mạnh lưỡi kiếm rộng xuống, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Augusta nhảy lên rồi đập mạnh lưỡi kiếm rộng xuống, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25816,7 +25816,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Augusta: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Augusta: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25881,7 +25881,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Augusta quét lưỡi kiếm rộng về phía trước, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack.</t>
+          <t>Augusta quét lưỡi kiếm rộng về phía trước, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;, được tính là Sát Thương Tấn Công Mạnh.</t>
         </is>
       </c>
     </row>
@@ -25946,7 +25946,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Augusta: Hướng dẫn &lt;color=#d4bf5f&gt;Chain Heavy Attack&lt;/color&gt; 2</t>
+          <t>Augusta: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack Liên Hoàn&lt;/color&gt; 2</t>
         </is>
       </c>
     </row>
@@ -26011,7 +26011,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Prowess&lt;/color&gt; đạt tối đa, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nhảy&lt;/color&gt; ngay sau khi thi triển &lt;color=Highlight&gt;Resonance Skill - Warrior's Blade&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và tiêu hao toàn bộ Uy Lực.</t>
+          <t>Khi &lt;color=Highlight&gt;Uy Lực&lt;/color&gt; đạt tối đa, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nhảy&lt;/color&gt; ngay sau khi thi triển &lt;color=Highlight&gt;Resonance Skill - Lưỡi Kiếm Chiến Binh&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Đòn Heavy Attack - Hồi Sấm: Đấm Móc Lên&lt;/color&gt;, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; và tiêu hao toàn bộ Uy Lực.</t>
         </is>
       </c>
     </row>
@@ -26076,7 +26076,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Augusta: &lt;color=#d4bf5f&gt;Chain Heavy Attack&lt;/color&gt;</t>
+          <t>Augusta: &lt;color=#d4bf5f&gt;Hướng dẫn Kết Hợp Heavy Attack (3)&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26141,7 +26141,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Prowess&lt;/color&gt; đạt tối đa, &lt;color=Highlight&gt;release&lt;/color&gt; hoặc &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack again&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nhảy&lt;/color&gt; trong khoảng thời gian nhất định sau khi thi triển &lt;color=Highlight&gt;Heavy Attack - Steelclash&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và tiêu hao toàn bộ Uy Lực.</t>
+          <t>Khi &lt;color=Highlight&gt;Uy Lực&lt;/color&gt; đạt tối đa, &lt;color=Highlight&gt;thả&lt;/color&gt; hoặc &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Đòn Normal Attack lại&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nhảy&lt;/color&gt; trong khoảng thời gian nhất định sau khi thi triển &lt;color=Highlight&gt;Đòn Heavy Attack - Va Đập Thép&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Đòn Heavy Attack - Hồi Sấm: Đấm Móc Lên&lt;/color&gt;, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; và tiêu hao toàn bộ Uy Lực.</t>
         </is>
       </c>
     </row>
@@ -26206,7 +26206,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Augusta: &lt;color=#d4bf5f&gt;Chain Resonance Skill&lt;/color&gt;</t>
+          <t>Augusta: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Kết Hợp&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26273,9 +26273,9 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Ascendancy&lt;/color&gt; đạt tối đa:
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill liên tục để thi triển các kỹ năng theo thứ tự:
-&lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Strike&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Leap&lt;/color&gt;, và &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Plunge&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Thăng Hoa&lt;/color&gt; đạt tối đa:
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Skill liên tục để thi triển các kỹ năng theo thứ tự:
+&lt;color=Highlight&gt;Resonance Skill - Ánh Dương Bất Tử: Đòn Đánh&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Ánh Dương Bất Tử: Nhảy Tấn Công&lt;/color&gt;, và &lt;color=Highlight&gt;Resonance Skill - Ánh Dương Bất Tử: Lao Xuống&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26340,7 +26340,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Augusta: &lt;color=#d4bf5f&gt;Chain Resonance Liberation&lt;/color&gt;</t>
+          <t>Augusta: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation Kết Hợp&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26406,8 +26406,8 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Với 2 tầng &lt;color=Highlight&gt;Majesty&lt;/color&gt;, &lt;color=Highlight&gt;giữ Resonance Liberation&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Resonance Liberation - Sublime is the Sun&lt;/color&gt;.
-Thi triển &lt;color=Highlight&gt;Resonance Liberation - Sublime is the Sun&lt;/color&gt; sẽ tạo ra &lt;color=Highlight&gt;Ruler's Realm&lt;/color&gt; và đưa Augusta vào trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt;, thời gian sẽ ngừng trôi và &lt;color=Highlight&gt;chuyển đổi Resonator bị vô hiệu hóa&lt;/color&gt;. Chỉ có thể thi triển &lt;color=Highlight&gt;Sublime is the Sun - Sunborne&lt;/color&gt; và &lt;color=Highlight&gt;Sublime is the Sun - Everbright Protector&lt;/color&gt; trong hướng dẫn này.</t>
+          <t>Với 2 tầng &lt;color=Highlight&gt;Oai Phong&lt;/color&gt;, &lt;color=Highlight&gt;giữ Liberation Cộng Hưởng&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Liberation Cộng Hưởng - Vầng Thái Dương Vĩ Đại&lt;/color&gt;.
+Thi triển &lt;color=Highlight&gt;Liberation Cộng Hưởng - Vầng Thái Dương Vĩ Đại&lt;/color&gt; sẽ tạo ra &lt;color=Highlight&gt;Cõi Lãnh Chúa&lt;/color&gt; và đưa Augusta vào trạng thái &lt;color=Highlight&gt;Thề Trung Thành&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;Thề Trung Thành&lt;/color&gt;, thời gian sẽ ngừng trôi và &lt;color=Highlight&gt;không thể chuyển đổi Resonator&lt;/color&gt;. Chỉ có thể thi triển &lt;color=Highlight&gt;Vầng Thái Dương Vĩ Đại - Hóa Thân Mặt Trời&lt;/color&gt; và &lt;color=Highlight&gt;Vầng Thái Dương Vĩ Đại - Người Bảo Vệ Vĩnh Hằng&lt;/color&gt; trong hướng dẫn này.</t>
         </is>
       </c>
     </row>
@@ -26602,7 +26602,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Heavy Attack Trên Không</t>
+          <t>Đòn Tấn Công Mạnh Trên Không</t>
         </is>
       </c>
     </row>
@@ -26667,7 +26667,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Nhấn {0}/{1} trên không để kích hoạt &lt;color=#ffd12f&gt;backflip&lt;/color&gt;.</t>
+          <t>Nhấn {0}/{1} trên không để kích hoạt &lt;color=#ffd12f&gt;lộn ngược&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26732,7 +26732,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Nhấn Dodge giữa không trung để thực hiện &lt;color=#ffd12f&gt;backflip&lt;/color&gt;.</t>
+          <t>Nhấn Né Tránh giữa không trung để thực hiện &lt;color=#ffd12f&gt;lộn ngược&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26797,7 +26797,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Nhấn {0} để dùng Kỹ Năng Basic</t>
+          <t>Nhấn {0} để dùng Kỹ Năng Cơ Bản</t>
         </is>
       </c>
     </row>
@@ -26862,7 +26862,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Đang nạp Concerto Energy.221&lt;subnode=FightConcertoState1/&gt; &lt;subnode=FightConcertoState2/&gt; &lt;subnode=FightConcertoState3/&gt;</t>
+          <t>Đang nạp Năng lượng Concerto.221&lt;subnode=FightConcertoState1/&gt; &lt;subnode=FightConcertoState2/&gt; &lt;subnode=FightConcertoState3/&gt;</t>
         </is>
       </c>
     </row>
@@ -27057,7 +27057,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Khi đang ở trên không, nhấn {0}/{1} để kích hoạt &lt;color=#ffd12f&gt;Mid-Air Dodge&lt;/color&gt;.</t>
+          <t>Khi đang ở trên không, nhấn {0}/{1} để kích hoạt &lt;color=#ffd12f&gt;Né Tránh Giữa Không&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27252,7 +27252,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>{0} Giữ để tung **Heavy Attack**.</t>
+          <t>Giữ để tung đòn Heavy Attack.</t>
         </is>
       </c>
     </row>
@@ -27317,7 +27317,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Nhấn {0}/{1} ngay để kích hoạt &lt;color=#ffd12f&gt;Dodge&lt;/color&gt;</t>
+          <t>Nhấn {0}/{1} ngay để kích hoạt &lt;color=#ffd12f&gt;Né Tránh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -27382,7 +27382,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Outro Skill của Chixia sẽ kích hoạt một vụ nổ</t>
+          <t>Kỹ năng Outro của Chixia sẽ kích hoạt một vụ nổ</t>
         </is>
       </c>
     </row>
@@ -27447,7 +27447,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Outro Skill của Chixia sẽ kích hoạt một vụ nổ</t>
+          <t>Kỹ năng Outro của Chixia sẽ kích hoạt một vụ nổ</t>
         </is>
       </c>
     </row>
@@ -27512,7 +27512,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Kỹ Năng Kết Thúc của Rover sẽ tạo ra một vùng trì trệ.</t>
+          <t>Outro Skill của Rover sẽ tạo ra một vùng trì trệ.</t>
         </is>
       </c>
     </row>
@@ -27577,7 +27577,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Kỹ Năng Kết Thúc của Rover sẽ tạo ra một vùng trì trệ.</t>
+          <t>Outro Skill của Rover sẽ tạo ra một vùng trì trệ.</t>
         </is>
       </c>
     </row>
@@ -27642,7 +27642,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Stand gần Đèn Cảm Ứng và nhấn {0} để kích hoạt.</t>
+          <t>Đứng gần Đèn Cảm Ứng và nhấn {0} để kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -27708,8 +27708,8 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Giữ {0} và {1}/{2} gần tường để thực hiện &lt;color=#ffd12f&gt;Wall Dash&lt;/color&gt;.
-Wall Dash tiêu hao &lt;color=#ffd12f&gt;STA&lt;/color&gt; và tự động dừng khi STA cạn kiệt.</t>
+          <t>Giữ {0} và {1}/{2} gần tường để thực hiện &lt;color=#ffd12f&gt;Đột Kích Tường&lt;/color&gt;.
+Đột Kích Tường tiêu hao &lt;color=#ffd12f&gt;STA&lt;/color&gt; và tự động dừng khi STA cạn kiệt.</t>
         </is>
       </c>
     </row>
@@ -27774,7 +27774,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Nhấn {0} để dùng &lt;color=#ffd12f&gt;Basic Attack&lt;/color&gt;.</t>
+          <t>Nhấn {0} để dùng &lt;color=#ffd12f&gt;Đòn Cơ Bản&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27905,8 +27905,8 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt &lt;color=#ffd12f&gt;Resonance Beacon&lt;/color&gt;, bạn có thể mở Map và &lt;color=#ffd12f&gt;fast travel&lt;/color&gt; đến bất kỳ Resonance Beacon nào đã kích hoạt.
-Hãy đến Trạm Resonance để &lt;color=#ffd12f&gt;heal&lt;/color&gt; Resonators bị thương hoặc bất tỉnh.</t>
+          <t>Sau khi kích hoạt &lt;color=#ffd12f&gt;Điểm Cộng Hưởng&lt;/color&gt;, bạn có thể mở Bản Đồ và &lt;color=#ffd12f&gt;dịch chuyển tức thời&lt;/color&gt; đến bất kỳ Điểm Cộng Hưởng nào đã kích hoạt.
+Hãy đến Trạm Cộng Hưởng để &lt;color=#ffd12f&gt;hồi phục&lt;/color&gt; Resonator bị thương hoặc bất tỉnh.</t>
         </is>
       </c>
     </row>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Resonance Nexus&lt;/color&gt; lưu trữ thông tin về khu vực xung quanh. Kích hoạt nó để nhận dữ liệu &lt;color=#ffd12f&gt;Map&lt;/color&gt; tương ứng.</t>
+          <t>&lt;color=#ffd12f&gt;Nexus Cộng Hưởng&lt;/color&gt; lưu trữ thông tin về khu vực xung quanh. Kích hoạt nó để nhận dữ liệu &lt;color=#ffd12f&gt;Bản Đồ&lt;/color&gt; tương ứng.</t>
         </is>
       </c>
     </row>
@@ -28036,7 +28036,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Đến Trạm Resonance để &lt;color=#ffd12f&gt;heal&lt;/color&gt; Resonators bị thương hoặc bất tỉnh.</t>
+          <t>Đến Trạm Cộng Hưởng để &lt;color=#ffd12f&gt;hồi phục&lt;/color&gt; Resonator bị thương hoặc bất tỉnh.</t>
         </is>
       </c>
     </row>
@@ -28101,7 +28101,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Khi kẻ địch sắp sử dụng một số chiêu thức, một &lt;color=#ffd12f&gt;Weakness Halo&lt;/color&gt; sẽ xuất hiện. Attack kịp thời để kích hoạt &lt;color=#ffd12f&gt;Counterattack&lt;/color&gt;, chặn đứng đòn tấn công và giành thế thượng phong.</t>
+          <t>Khi kẻ địch sắp sử dụng một số chiêu thức, một &lt;color=#ffd12f&gt;Vầng Halo Yếu Điểm&lt;/color&gt; sẽ xuất hiện. Tấn công kịp thời để kích hoạt &lt;color=#ffd12f&gt;Phản Đòn&lt;/color&gt;, chặn đứng đòn tấn công và giành thế thượng phong.</t>
         </is>
       </c>
     </row>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Thực hiện Dodge đúng thời điểm để tránh các đòn tấn công của kẻ địch. Một lần &lt;color=#ffd12f&gt;Dodge&lt;/color&gt; thành công sẽ tạm thời miễn nhiễm &lt;color=#ffd12f&gt;DMG&lt;/color&gt;, cho phép bạn thực hiện &lt;color=#ffd12f&gt;Dodge Counter&lt;/color&gt; trong &lt;color=#ffd12f&gt;Basic Attack&lt;/color&gt; tiếp theo.</t>
+          <t>Né tránh đúng lúc để tránh đòn tấn công của kẻ địch. Một lần &lt;color=#ffd12f&gt;Né tránh&lt;/color&gt; thành công sẽ tạm thời miễn nhiễm sát thương, cho phép bạn thực hiện &lt;color=#ffd12f&gt;Dodge Counter Tránh&lt;/color&gt; trong Đòn Basic Attack tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -28231,7 +28231,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Gây sát thương để giảm &lt;color=#ffd12f&gt;Vibration Strength&lt;/color&gt; của kẻ địch. &lt;color=#ffd12f&gt;Counterattack&lt;/color&gt; sẽ giảm mạnh Vibration Strength của chúng. Khi Vibration Strength cạn kiệt, kẻ địch sẽ bị &lt;color=#ffd12f&gt;Immobilized&lt;/color&gt; và không thể hành động trong một khoảng thời gian.</t>
+          <t>Gây sát thương để giảm &lt;color=#ffd12f&gt;Sức Rung Động&lt;/color&gt; của kẻ địch. &lt;color=#ffd12f&gt;Phản Đòn&lt;/color&gt; sẽ giảm mạnh Sức Rung Động của chúng. Khi Sức Rung Động cạn kiệt, kẻ địch sẽ bị &lt;color=#ffd12f&gt;Bất Động&lt;/color&gt; và không thể hành động trong một khoảng thời gian.</t>
         </is>
       </c>
     </row>
@@ -28296,7 +28296,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Khi kẻ địch ở trạng thái &lt;color=#b49f50&gt;Immobilized&lt;/color&gt;, bạn có thể sử dụng &lt;color=#b49f50&gt;Finishing Attack&lt;/color&gt; để gây sát thương lớn. Sau khi nhận Đòn Kết Liễu, chúng sẽ hồi phục khỏi trạng thái Bất Động.</t>
+          <t>Khi kẻ địch ở trạng thái &lt;color=#b49f50&gt;Bất Động&lt;/color&gt;, bạn có thể sử dụng &lt;color=#b49f50&gt;Đòn Kết Liễu&lt;/color&gt; để gây sát thương lớn. Sau khi nhận Đòn Kết Liễu, chúng sẽ hồi phục khỏi trạng thái Bất Động.</t>
         </is>
       </c>
     </row>
@@ -28361,7 +28361,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Mô-đun &lt;color=#ffd12f&gt;Sensor&lt;/color&gt; trong Công cụ giúp phát hiện nội dung giá trị trong cảnh, như &lt;color=#ffd12f&gt;collectibles&lt;/color&gt;, &lt;color=#ffd12f&gt;enemy weaknesses&lt;/color&gt;, v.v.</t>
+          <t>Mô-đun &lt;color=#ffd12f&gt;Cảm Biến&lt;/color&gt; trong Tiện Ích giúp phát hiện nội dung giá trị trong cảnh, như &lt;color=#ffd12f&gt;vật phẩm thu thập&lt;/color&gt;, &lt;color=#ffd12f&gt;điểm yếu của kẻ địch&lt;/color&gt;, v.v.</t>
         </is>
       </c>
     </row>
@@ -28427,8 +28427,8 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Resonators tích lũy &lt;color=#ffd12f&gt;Concerto Energy&lt;/color&gt; khi gây sát thương hoặc Dodge trong chiến đấu.
-Khi Concerto Energy đầy, biểu tượng của Resonators khác sẽ sáng lên.</t>
+          <t>Resonator tích lũy &lt;color=#ffd12f&gt;Năng Lượng Giao Hưởng&lt;/color&gt; khi gây sát thương hoặc né tránh trong chiến đấu.
+Khi Năng Lượng Giao Hưởng đầy, biểu tượng của các Resonator khác sẽ sáng lên.</t>
         </is>
       </c>
     </row>
@@ -28493,7 +28493,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Khi đạt đến &lt;color=#ffd12f&gt;SOL3 Giai đoạn&lt;/color&gt; cao hơn, ngươi sẽ có cơ hội nhận thêm &lt;color=#ffd12f&gt;rewards&lt;/color&gt; sau khi đánh bại kẻ địch hoặc hoàn thành Echo Sonoro. Tuy nhiên, hãy cẩn thận, vì kẻ địch ngươi gặp cũng sẽ &lt;color=#ffd12f&gt;dangerous&lt;/color&gt; hơn, và ngược lại.</t>
+          <t>Khi đạt đến &lt;color=#ffd12f&gt;Giai Đoạn SOL3&lt;/color&gt; cao hơn, ngươi sẽ có cơ hội nhận thêm &lt;color=#ffd12f&gt;phần thưởng&lt;/color&gt; sau khi đánh bại kẻ địch hoặc hoàn thành Tổ Tacet Sonoro. Tuy nhiên, hãy cẩn thận, vì kẻ địch ngươi gặp cũng sẽ &lt;color=#ffd12f&gt;nguy hiểm&lt;/color&gt; hơn, và ngược lại.</t>
         </is>
       </c>
     </row>
@@ -28558,7 +28558,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Sau khi dọn sạch các Tacet Field, bạn có thể dùng Waveplate để nhận các nguyên liệu phát triển Echoes đa dạng và &lt;color=#ffd12f&gt;collected Echoes&lt;/color&gt; của bộ Sonata tương ứng.</t>
+          <t>Sau khi dọn sạch các Tổ Tacet, bạn có thể dùng Waveplate để nhận các nguyên liệu phát triển Echo đa dạng và &lt;color=#ffd12f&gt;Echo đã thu thập&lt;/color&gt; của bộ Sonata tương ứng.</t>
         </is>
       </c>
     </row>
@@ -28623,7 +28623,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Các Tacet Field sẽ hồi sinh theo chu kỳ, nên cậu có thể thách đấu nhiều lần để thu thập vật liệu. Nhưng lưu ý là cần tiêu tốn Waveplate để nhận được vật liệu nhé.</t>
+          <t>Các Tổ Tacet sẽ hồi sinh theo chu kỳ, nên cậu có thể thách đấu nhiều lần để thu thập vật liệu. Nhưng lưu ý là cần tiêu tốn Waveplate để nhận được vật liệu nhé.</t>
         </is>
       </c>
     </row>
@@ -28688,7 +28688,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Simulation Training Ground nằm tại Jinzhou. Hoàn thành các thử thách để thu thập vật liệu cần thiết cho việc nâng cấp và phát triển Resonator. Increase &lt;color=#ffd12f&gt;SOL3 Giai đoạn&lt;/color&gt; để mở khóa thêm những thử thách có phần thưởng hấp dẫn hơn.</t>
+          <t>Khu Huấn Luyện Mô Phỏng nằm tại Jinzhou. Hoàn thành các thử thách để thu thập vật liệu cần thiết cho việc nâng cấp và phát triển Resonator. Tăng &lt;color=#ffd12f&gt;Giai Đoạn SOL3&lt;/color&gt; để mở khóa thêm những thử thách có phần thưởng hấp dẫn hơn.</t>
         </is>
       </c>
     </row>
@@ -28753,7 +28753,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Một mục tiêu huấn luyện thông minh phổ biến. Mỗi mục tiêu có &lt;color=#ffd12f&gt;training rules&lt;/color&gt; khác nhau. Sau khi kích hoạt, drone sẽ được phóng ra. Đánh trúng tất cả drone để hoàn thành huấn luyện.</t>
+          <t>Một mục tiêu huấn luyện thông minh phổ biến. Mỗi mục tiêu có &lt;color=#ffd12f&gt;quy tắc huấn luyện&lt;/color&gt; khác nhau. Sau khi kích hoạt, drone sẽ được phóng ra. Đánh trúng tất cả drone để hoàn thành huấn luyện.</t>
         </is>
       </c>
     </row>
@@ -28823,12 +28823,12 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Tích lũy &lt;color=#ffd12f&gt;Union EXP&lt;/color&gt; để tăng &lt;color=#ffd12f&gt;Cấp Liên Minh&lt;/color&gt; và mở khóa thêm nhiệm vụ cùng hoạt động.
-Bạn có thể nhanh chóng nhận Union EXP qua các cách sau: 
-I. Hoàn thành nhiệm vụ &lt;color=#ffd12f&gt;Daily Activity&lt;/color&gt;.
-II. &lt;color=#ffd12f&gt;Consume Waveplates&lt;/color&gt;.
-III. &lt;color=#ffd12f&gt;Complete various quests&lt;/color&gt;.
-IV. &lt;color=#ffd12f&gt;Mở Supply Chests&lt;/color&gt; và hoàn thành các hoạt động trong thế giới mở.</t>
+          <t>Tích lũy &lt;color=#ffd12f&gt;Kinh Nghiệm Liên Minh&lt;/color&gt; để tăng &lt;color=#ffd12f&gt;Cấp Độ Liên Minh&lt;/color&gt; và mở khóa thêm nhiệm vụ cùng hoạt động.
+Bạn có thể nhanh chóng nhận Kinh Nghiệm Liên Minh qua các cách sau: 
+I. Hoàn thành nhiệm vụ &lt;color=#ffd12f&gt;Hoạt Động Hằng Ngày&lt;/color&gt;.
+II. &lt;color=#ffd12f&gt;Tiêu thụ Waveplate&lt;/color&gt;.
+III. &lt;color=#ffd12f&gt;Hoàn thành các nhiệm vụ khác nhau&lt;/color&gt;.
+IV. &lt;color=#ffd12f&gt;Mở Rương Cung Ứng&lt;/color&gt; và hoàn thành các hoạt động trong thế giới mở.</t>
         </is>
       </c>
     </row>
@@ -28893,7 +28893,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Hấp thụ Echoes để tăng cấp Data Bank. Cấp càng cao, &lt;color=#ffd12f&gt;Drop Rate&lt;/color&gt; của Echoes càng lớn và &lt;color=#ffd12f&gt;max absorbable Rarity&lt;/color&gt; càng cao.</t>
+          <t>Hấp thụ Echo để tăng cấp Ngân Hàng Dữ Liệu. Cấp càng cao, &lt;color=#ffd12f&gt;Tỷ Lệ Rơi&lt;/color&gt; của Echo càng lớn và &lt;color=#ffd12f&gt;Độ Hiếm tối đa có thể hấp thụ&lt;/color&gt; càng cao.</t>
         </is>
       </c>
     </row>
@@ -29023,7 +29023,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Sau khi nhặt &lt;color=#ffd12f&gt;Tacetite Fulminate&lt;/color&gt;, cậu có thể Dodgem &lt;color=#ffd12f&gt;directly&lt;/color&gt; vào mục tiêu hoặc dùng &lt;color=#ffd12f&gt;Aim&lt;/color&gt; để &lt;color=#ffd12f&gt;precisely control&lt;/color&gt; vị trí rơi. Khi Dodgem ra, Tacetite Fulminate sẽ gây ra một vụ nổ dữ dội.</t>
+          <t>Sau khi nhặt &lt;color=#ffd12f&gt;Tacetite Fulminate&lt;/color&gt;, cậu có thể ném &lt;color=#ffd12f&gt;trực tiếp&lt;/color&gt; vào mục tiêu hoặc dùng &lt;color=#ffd12f&gt;Ngắm&lt;/color&gt; để &lt;color=#ffd12f&gt;điều khiển chính xác&lt;/color&gt; vị trí rơi. Khi ném ra, Tacetite Fulminate sẽ gây ra một vụ nổ dữ dội.</t>
         </is>
       </c>
     </row>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Gây sát thương để giảm Strength Dao Động của kẻ địch. Khi Strength Dao Động về 0, kẻ địch sẽ bị &lt;color=#8c7e51&gt;Immobilized&lt;/color&gt;.</t>
+          <t>Gây sát thương để giảm Sức Mạnh Dao Động của kẻ địch. Khi Sức Mạnh Dao Động về 0, kẻ địch sẽ bị &lt;color=#8c7e51&gt;Bất Động&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29153,7 +29153,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Resonators tích lũy Concerto Energy khi gây sát thương hoặc Dodge trong chiến đấu. Khi Concerto Energy đầy, hãy chuyển đổi Resonators để tiêu hao toàn bộ Concerto Energy, kích hoạt Kỹ Năng Kết Thúc của Resonators rời đi và đồng thời kích hoạt Kỹ Năng Khởi Đầu của Resonators mới vào.</t>
+          <t>Resonator tích lũy Năng Lượng Giao Hưởng khi gây sát thương hoặc né tránh trong chiến đấu. Khi Năng Lượng Giao Hưởng đầy, hãy chuyển đổi Resonator để tiêu hao toàn bộ Năng Lượng Giao Hưởng, kích hoạt Outro Skill của Resonator rời đi và đồng thời kích hoạt Kỹ Năng Khởi Đầu của Resonator mới vào.</t>
         </is>
       </c>
     </row>
@@ -29218,7 +29218,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=#ffd12f&gt;Counterattacks&lt;/color&gt; và &lt;color=#ffd12f&gt;Dodge Counters&lt;/color&gt; để chặn đứng hành động của kẻ địch.</t>
+          <t>Sử dụng &lt;color=#ffd12f&gt;Phản Đòn&lt;/color&gt; và &lt;color=#ffd12f&gt;Dodge Counter Tránh&lt;/color&gt; để chặn đứng hành động của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -29283,7 +29283,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Hầu hết các đòn tấn công của kẻ địch đều có thể bị chặn lại bằng &lt;color=#ffd12f&gt;Counterattacks&lt;/color&gt;. Hãy thường xuyên sử dụng Phản Đòn để giảm Concerto Vibrancy của kẻ địch và khiến nó rơi vào trạng thái &lt;color=#ffd12f&gt;Immobilized&lt;/color&gt;.</t>
+          <t>Hầu hết các đòn tấn công của kẻ địch đều có thể bị chặn lại bằng &lt;color=#ffd12f&gt;Phản Đòn&lt;/color&gt;. Hãy thường xuyên sử dụng Phản Đòn để giảm Sức Mạnh Rung Động của kẻ địch và khiến nó rơi vào trạng thái &lt;color=#ffd12f&gt;Bất Động&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29348,7 +29348,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Khi Impermanence Heron giơ cánh che đầu, nó sẽ chuyển sang trạng thái phòng thủ. Hãy dùng Intro Skill để giảm Concerto Vibrancy của nó, khiến nó rơi vào trạng thái &lt;color=#ffd12f&gt;Immobilized&lt;/color&gt;.</t>
+          <t>Khi Diệc Vô Thường giơ cánh che đầu, nó sẽ chuyển sang trạng thái phòng thủ. Hãy dùng Kỹ Năng Khởi Động để giảm Sức Mạnh Rung Động của nó, khiến nó rơi vào trạng thái &lt;color=#ffd12f&gt;Bất Động&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29413,7 +29413,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Các đòn tấn công túm gây sát thương cực lớn. Hãy dùng &lt;color=#ffd12f&gt;Counterattacks&lt;/color&gt; để chặn các đòn túm này.</t>
+          <t>Các đòn tấn công túm gây sát thương cực lớn. Hãy dùng &lt;color=#ffd12f&gt;Phản Đòn&lt;/color&gt; để chặn các đòn túm này.</t>
         </is>
       </c>
     </row>
@@ -29543,7 +29543,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Sau khi hấp thụ &lt;color=#ffd12f&gt;Prisms&lt;/color&gt; của các thuộc tính khác nhau, Heron sẽ &lt;color=#ffd12f&gt;recover all its HP&lt;/color&gt; và bước vào trạng thái &lt;color=#ffd12f&gt;enpowered state&lt;/color&gt; tương ứng. Heron được tăng cường sẽ tung ra những đòn tấn công dữ dội hơn.</t>
+          <t>Sau khi hấp thụ &lt;color=#ffd12f&gt;Lăng Kính&lt;/color&gt; của các thuộc tính khác nhau, Heron sẽ &lt;color=#ffd12f&gt;hồi phục toàn bộ HP&lt;/color&gt; và bước vào trạng thái &lt;color=#ffd12f&gt;cường hóa&lt;/color&gt; tương ứng. Heron được tăng cường sẽ tung ra những đòn tấn công dữ dội hơn.</t>
         </is>
       </c>
     </row>
@@ -29608,7 +29608,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Sau khi hấp thụ &lt;color=#ffd12f&gt;Prisms&lt;/color&gt; của các thuộc tính khác nhau, Heron sẽ &lt;color=#ffd12f&gt;recover all its HP&lt;/color&gt; và bước vào trạng thái &lt;color=#ffd12f&gt;enpowered state&lt;/color&gt; tương ứng. Heron được tăng cường sẽ tung ra những đòn tấn công dữ dội hơn.</t>
+          <t>Sau khi hấp thụ &lt;color=#ffd12f&gt;Lăng Kính&lt;/color&gt; của các thuộc tính khác nhau, Heron sẽ &lt;color=#ffd12f&gt;hồi phục toàn bộ HP&lt;/color&gt; và bước vào trạng thái &lt;color=#ffd12f&gt;cường hóa&lt;/color&gt; tương ứng. Heron được tăng cường sẽ tung ra những đòn tấn công dữ dội hơn.</t>
         </is>
       </c>
     </row>
@@ -29673,7 +29673,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Sau khi bước vào trạng thái điên cuồng, nó sẽ nhận được lá chắn và &lt;color=#ffd12f&gt;great DMG Reduction&lt;/color&gt;. Khi &lt;color=#ffd12f&gt;shield&lt;/color&gt; bị phá hủy, Vibration Strength của nó sẽ bị suy giảm nghiêm trọng.</t>
+          <t>Sau khi bước vào trạng thái điên cuồng, nó sẽ nhận được lá chắn và &lt;color=#ffd12f&gt;giảm DMG cực lớn&lt;/color&gt;. Khi &lt;color=#ffd12f&gt;lá chắn&lt;/color&gt; bị phá hủy, Sức Rung của nó sẽ bị suy giảm nghiêm trọng.</t>
         </is>
       </c>
     </row>
@@ -29738,7 +29738,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Khi Roseshroom bước vào trạng thái nạp, hãy nhắm vào &lt;color=#ffd12f&gt;core at its head&lt;/color&gt; bằng &lt;color=#ffd12f&gt;Pistols&lt;/color&gt; để làm giảm đáng kể Concerto Vibrancy của nó.</t>
+          <t>Khi Roseshroom bước vào trạng thái nạp, hãy nhắm vào &lt;color=#ffd12f&gt;lõi trên đầu nó&lt;/color&gt; bằng &lt;color=#ffd12f&gt;Súng Ngắn&lt;/color&gt; để làm giảm đáng kể Sức Mạnh Rung Động của nó.</t>
         </is>
       </c>
     </row>
@@ -29804,8 +29804,8 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Fusion Prism miễn nhiễm với sát thương &lt;color=#ffd12f&gt;Fusion&lt;/color&gt;. Nó cung cấp hiệu ứng tăng cường cho kẻ địch xung quanh, khiến sát thương chúng gây ra tăng mạnh.
-Fusion Prism có thể bị Cò Xanh và Cò Tím hấp thụ, mang lại bonus sát thương vĩnh viễn cho chúng sau khi hấp thụ.</t>
+          <t>Lăng Kính Fusion miễn nhiễm với DMG &lt;color=#ffd12f&gt;Fusion&lt;/color&gt;. Nó cung cấp hiệu ứng tăng cường cho kẻ địch xung quanh, khiến DMG chúng gây ra tăng mạnh.
+Lăng Kính Fusion có thể bị Cò Xanh và Cò Tím hấp thụ, mang lại bonus DMG vĩnh viễn cho chúng sau khi hấp thụ.</t>
         </is>
       </c>
     </row>
@@ -29871,8 +29871,8 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Glacio Prism miễn nhiễm với sát thương &lt;color=#ffd12f&gt;Glacio&lt;/color&gt;. Nó cung cấp hiệu ứng tăng cường cho kẻ địch xung quanh, giúp chúng có Trạng Thái Siêu Giáp (đòn tấn công không làm gián đoạn động tác).
-Glacio Prism có thể bị Cò Xanh và Cò Tím hấp thụ, mang lại Trạng Thái Siêu Giáp vĩnh viễn cho chúng sau khi hấp thụ.</t>
+          <t>Lăng Kính Glacio miễn nhiễm với DMG &lt;color=#ffd12f&gt;Glacio&lt;/color&gt;. Nó cung cấp hiệu ứng tăng cường cho kẻ địch xung quanh, giúp chúng có Trạng Thái Siêu Giáp (đòn tấn công không làm gián đoạn động tác).
+Lăng Kính Glacio có thể bị Cò Xanh và Cò Tím hấp thụ, mang lại Trạng Thái Siêu Giáp vĩnh viễn cho chúng sau khi hấp thụ.</t>
         </is>
       </c>
     </row>
@@ -29938,8 +29938,8 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Prism Spectro miễn nhiễm với sát thương &lt;color=#ffd12f&gt;Spectro&lt;/color&gt;. Nó cung cấp hiệu ứng hỗ trợ cho kẻ địch xung quanh, tạo khiên định kỳ cho chúng.
-Prism Spectro có thể bị Cò Xanh và Cò Tím hấp thụ, tạo khiên vĩnh viễn cho chúng sau khi hấp thụ.</t>
+          <t>Lăng Kính Spectro miễn nhiễm với DMG &lt;color=#ffd12f&gt;Spectro&lt;/color&gt;. Nó cung cấp hiệu ứng hỗ trợ cho kẻ địch xung quanh, tạo khiên định kỳ cho chúng.
+Lăng Kính Spectro có thể bị Cò Xanh và Cò Tím hấp thụ, tạo khiên vĩnh viễn cho chúng sau khi hấp thụ.</t>
         </is>
       </c>
     </row>
@@ -30005,8 +30005,8 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Echo Khải Hoang miễn nhiễm với sát thương &lt;color=#ffd12f&gt;Havoc&lt;/color&gt;. Nó cung cấp hiệu ứng tăng cường cho kẻ địch xung quanh, cho phép chúng tiêu hao Resonance Energy của Resonators bằng các đòn tấn công.
-Echo Khải Hoang có thể bị Cò Xanh và Cò Tím hấp thụ, mang lại hiệu ứng Tiêu Hao Năng Lượng vĩnh viễn cho chúng sau khi hấp thụ.</t>
+          <t>Tổ Tacet Khải Hoang miễn nhiễm với DMG &lt;color=#ffd12f&gt;Khải Hoang&lt;/color&gt;. Nó cung cấp hiệu ứng tăng cường cho kẻ địch xung quanh, cho phép chúng tiêu hao Resonance Energy của Resonator bằng các đòn tấn công.
+Tổ Tacet Khải Hoang có thể bị Cò Xanh và Cò Tím hấp thụ, mang lại hiệu ứng Tiêu Hao Năng Lượng vĩnh viễn cho chúng sau khi hấp thụ.</t>
         </is>
       </c>
     </row>
@@ -30071,7 +30071,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Các đòn tấn công của Resonators có thể phản xạ lại những ảo ảnh thương halberd và vòng cung ánh sáng từ Lioness of Glory, gây sát thương trở lại cho nó.</t>
+          <t>Các đòn tấn công của Resonator có thể phản xạ lại những ảo ảnh thương halberd và vòng cung ánh sáng từ Lioness of Glory, gây sát thương trở lại cho nó.</t>
         </is>
       </c>
     </row>
@@ -30136,7 +30136,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Khi Kerasaur hồi phục khỏi trạng thái Bất Động, nó sẽ có khả năng kháng cực cao với thuộc tính sát thương mà nó chịu nhiều nhất trước khi bị Bất Động.</t>
+          <t>Khi Kerasaur hồi phục khỏi trạng thái Bất Động, nó sẽ có khả năng kháng cực cao với thuộc tính DMG mà nó chịu nhiều nhất trước khi bị Bất Động.</t>
         </is>
       </c>
     </row>
@@ -30203,9 +30203,9 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Khi Cartethyia sử dụng &lt;color=#ffd12f&gt;Resonance Skill, Heavy Attack, or the final stage of a Basic Attack&lt;/color&gt;, cô sẽ triệu hồi Bóng Kiếm Đức Hạnh, Bóng Kiếm Bất Hòa và Bóng Kiếm Thần Thánh.
-Cartethyia có thể thu hồi ba Bóng Kiếm này khi thực hiện &lt;color=#ffd12f&gt;Plunging Attack&lt;/color&gt; để tăng sát thương của đòn tấn công này.
-Việc thu hồi Bóng Kiếm cũng sẽ ban cho cô &lt;color=Highlight&gt;Heart of Virtue&lt;/color&gt;, &lt;color=Highlight&gt;Power of Discord&lt;/color&gt; và &lt;color=Highlight&gt;Mandate of Divinity&lt;/color&gt; tương ứng, giúp tăng cường sức mạnh cho Cartethyia khi cô hóa thân thành Fleurdelys.</t>
+          <t>Khi Cartethyia sử dụng &lt;color=#ffd12f&gt;Resonance Skill, Đòn Heavy Attack hoặc giai đoạn cuối của Đòn Basic Attack&lt;/color&gt;, cô sẽ triệu hồi Bóng Kiếm Đức Hạnh, Bóng Kiếm Bất Hòa và Bóng Kiếm Thần Thánh.
+Cartethyia có thể thu hồi ba Bóng Kiếm này khi thực hiện &lt;color=#ffd12f&gt;Đòn Lao Xuống&lt;/color&gt; để tăng DMG của đòn tấn công này.
+Việc thu hồi Bóng Kiếm cũng sẽ ban cho cô &lt;color=Highlight&gt;Trái Tim Đức Hạnh&lt;/color&gt;, &lt;color=Highlight&gt;Sức Mạnh Bất Hòa&lt;/color&gt; và &lt;color=Highlight&gt;Thiên Mệnh Thần Thánh&lt;/color&gt; tương ứng, giúp tăng cường sức mạnh cho Cartethyia khi cô hóa thân thành Fleurdelys.</t>
         </is>
       </c>
     </row>
@@ -30272,7 +30272,7 @@
       <c r="M457" t="inlineStr">
         <is>
           <t>Khi kích hoạt Resonance Liberation, Cartethyia biến thành Fleurdelys và mở khóa các chiêu thức mới.
-Các đòn tấn công của Fleurdelys phục hồi Conviction. Khi Conviction đạt tối đa, {Cus:Ipt,Touch=tấn PC=press Gamepad=press} Resonance Liberation lần nữa để thi triển Lưỡi Kiếm Gió Hú, gây sát thương cực lớn.</t>
+Các đòn tấn công của Fleurdelys phục hồi Niềm Tin. Khi Niềm Tin đạt tối đa, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Liberation lần nữa để thi triển Lưỡi Kiếm Gió Hú, gây DMG cực lớn.</t>
         </is>
       </c>
     </row>
@@ -30338,8 +30338,8 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Thông qua đấu kiếm, cậu nhận được Resonance Duel, giúp tăng Cấp Độ Duel Sĩ và nhận nhiều phần thưởng giá trị. Số lượng Resonance Duel có thể nhận được mỗi tuần có giới hạn.
-Kỹ năng đấu kiếm của cậu được thể hiện qua Fame Flag. Mỗi chiến thắng sẽ mang lại cho cậu Fame Flag. Số lượng này không giới hạn.</t>
+          <t>Thông qua đấu kiếm, cậu nhận được Cộng Hưởng Đấu, giúp tăng Cấp Độ Đấu Sĩ và nhận nhiều phần thưởng giá trị. Số lượng Cộng Hưởng Đấu có thể nhận được mỗi tuần có giới hạn.
+Kỹ năng đấu kiếm của cậu được thể hiện qua Cờ Danh Vọng. Mỗi chiến thắng sẽ mang lại cho cậu Cờ Danh Vọng. Số lượng này không giới hạn.</t>
         </is>
       </c>
     </row>
@@ -30404,7 +30404,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Touch vào &lt;color=#ffd12f&gt;signs&lt;/color&gt; để hồi một lượng &lt;color=#ffd12f&gt;STA&lt;/color&gt; nhất định.</t>
+          <t>Chạm vào &lt;color=#ffd12f&gt;dấu hiệu&lt;/color&gt; để hồi một lượng &lt;color=#ffd12f&gt;STA&lt;/color&gt; nhất định.</t>
         </is>
       </c>
     </row>
@@ -30469,7 +30469,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt, nó sẽ triệu hồi kẻ địch dưới dạng ảo ảnh. &lt;color=#ffd12f&gt;Defeat&lt;/color&gt; tất cả &lt;color=#ffd12f&gt;enemies&lt;/color&gt; để hoàn thành thử thách và nhận phần thưởng.</t>
+          <t>Sau khi kích hoạt, nó sẽ triệu hồi kẻ địch dưới dạng ảo ảnh. &lt;color=#ffd12f&gt;Đánh bại&lt;/color&gt; tất cả &lt;color=#ffd12f&gt;kẻ địch&lt;/color&gt; để hoàn thành thử thách và nhận phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt, &lt;color=#ffd12f&gt;reach the finish line&lt;/color&gt; hoặc &lt;color=#ffd12f&gt;collect a certain amount of Mục tiêu Points&lt;/color&gt; trong thời gian quy định để nhận phần thưởng tương ứng.</t>
+          <t>Sau khi kích hoạt, &lt;color=#ffd12f&gt;về đích&lt;/color&gt; hoặc &lt;color=#ffd12f&gt;thu thập đủ số lượng Điểm Mục Tiêu&lt;/color&gt; trong thời gian quy định để nhận phần thưởng tương ứng.</t>
         </is>
       </c>
     </row>
@@ -30599,7 +30599,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Khi Resonator đang ở trạng thái &lt;color=#ffd12f&gt;Mô-đun: Slow&lt;/color&gt;, lượng STA tiêu hao sẽ tăng lên và &lt;color=#ffd12f&gt;Movement Speed will be reduced&lt;/color&gt;.</t>
+          <t>Khi Resonator đang ở trạng thái &lt;color=#ffd12f&gt;Mô-đun: Chậm&lt;/color&gt;, lượng STA tiêu hao sẽ tăng lên và &lt;color=#ffd12f&gt;Tốc Độ Di Chuyển của họ sẽ bị giảm&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30665,8 +30665,8 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Sau khi nhặt một Quả Nổ, cậu có thể Dodgem nó ra xa để kích nổ. Bằng cách &lt;color=#ffd12f&gt;Aiming&lt;/color&gt;, cậu có thể &lt;color=#ffd12f&gt;precisely control&lt;/color&gt; điểm rơi.
-Quả Nổ nằm trên mặt đất không thể điều khiển bằng Levitator, nhưng cậu có thể &lt;color=#ffd12f&gt;attack&lt;/color&gt; trực tiếp để kích hoạt &lt;color=#ffd12f&gt;explosion&lt;/color&gt;.</t>
+          <t>Sau khi nhặt một Quả Nổ, cậu có thể ném nó ra xa để kích nổ. Bằng cách &lt;color=#ffd12f&gt;Ngắm&lt;/color&gt;, cậu có thể &lt;color=#ffd12f&gt;điều khiển chính xác&lt;/color&gt; điểm rơi.
+Quả Nổ nằm trên mặt đất không thể điều khiển bằng Levitator, nhưng cậu có thể &lt;color=#ffd12f&gt;tấn công&lt;/color&gt; trực tiếp để kích hoạt &lt;color=#ffd12f&gt;vụ nổ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30731,7 +30731,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=#ffd12f&gt;Plunging Attacks&lt;/color&gt; để đánh vào cơ chế dưới đất, khớp các mẫu ngẫu nhiên với &lt;color=#ffd12f&gt;Mục tiêu Patterns&lt;/color&gt;.</t>
+          <t>Sử dụng &lt;color=#ffd12f&gt;Đòn Lao Xuống&lt;/color&gt; để đánh vào cơ chế dưới đất, khớp các mẫu ngẫu nhiên với &lt;color=#ffd12f&gt;Mẫu Mục Tiêu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30796,7 +30796,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Sau khi thử thách bắt đầu, hãy sử dụng &lt;color=#ffd12f&gt;Explosive Charges&lt;/color&gt; và các phương tiện khác một cách hợp lý để &lt;color=#ffd12f&gt;hit&lt;/color&gt; càng nhiều &lt;color=#ffd12f&gt;targets&lt;/color&gt; càng tốt.</t>
+          <t>Sau khi thử thách bắt đầu, hãy sử dụng &lt;color=#ffd12f&gt;Bom Nổ&lt;/color&gt; và các phương tiện khác một cách hợp lý để &lt;color=#ffd12f&gt;tấn công&lt;/color&gt; càng nhiều &lt;color=#ffd12f&gt;mục tiêu&lt;/color&gt; càng tốt.</t>
         </is>
       </c>
     </row>
@@ -30863,9 +30863,9 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Khi ở trong Khu Vực Challenge, &lt;color=#ffd12f&gt;Glory Level&lt;/color&gt; của bạn sẽ hiển thị ở góc trên bên trái màn hình.
-Tìm và đánh bại Tacet Discord hoặc chiếm giữ Cờ Chinh Phục để nhận Points Săn. Points Săn dùng để tăng Cấp Độ Glory và nhận các hiệu ứng tăng cường.
-Độ khó của thử thách sẽ giảm khi khoảng cách Cấp Độ Glory giữa bạn và kẻ địch thu hẹp.</t>
+          <t>Khi ở trong Khu Vực Thử Thách, &lt;color=#ffd12f&gt;Cấp Độ Vinh Quang&lt;/color&gt; của bạn sẽ hiển thị ở góc trên bên trái màn hình.
+Tìm và đánh bại Tacet Discord hoặc chiếm giữ Cờ Chinh Phục để nhận Điểm Săn. Điểm Săn dùng để tăng Cấp Độ Vinh Quang và nhận các hiệu ứng tăng cường.
+Độ khó của thử thách sẽ giảm khi khoảng cách Cấp Độ Vinh Quang giữa bạn và kẻ địch thu hẹp.</t>
         </is>
       </c>
     </row>
@@ -30931,8 +30931,8 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Thử thách không kết thúc khi cậu bị hạ gục trong Khu Vực Thi Đấu, nhưng Cấp Độ Glory của cậu sẽ giảm xuống bằng với &lt;color=#ffd12f&gt;Trial Level&lt;/color&gt;. Tuy nhiên, cậu sẽ nhận được thêm Points Săn, và phần thưởng này sẽ tiếp tục có hiệu lực cho đến khi Cấp Độ Glory của cậu phục hồi về mức cao nhất từng đạt được. Hãy lưu ý điều này khi đối đầu với những đối thủ mạnh nhé.
-Cậu có thể kiếm Points Trial bằng cách chiếm giữ các Cờ Chinh Phục. Points Trial sẽ tăng Cấp Độ Trial của cậu, chỉ có hiệu lực trong cuộc thi này và không bị reset khi cậu bị hạ gục.</t>
+          <t>Thử thách không kết thúc khi cậu bị hạ gục trong Khu Vực Thi Đấu, nhưng Cấp Độ Vinh Quang của cậu sẽ giảm xuống bằng với &lt;color=#ffd12f&gt;Cấp Độ Thử Thách&lt;/color&gt;. Tuy nhiên, cậu sẽ nhận được thêm Điểm Săn, và phần thưởng này sẽ tiếp tục có hiệu lực cho đến khi Cấp Độ Vinh Quang của cậu phục hồi về mức cao nhất từng đạt được. Hãy lưu ý điều này khi đối đầu với những đối thủ mạnh nhé.
+Cậu có thể kiếm Điểm Thử Thách bằng cách chiếm giữ các Cờ Chinh Phục. Điểm Thử Thách sẽ tăng Cấp Độ Thử Thách của cậu, chỉ có hiệu lực trong cuộc thi này và không bị reset khi cậu bị hạ gục.</t>
         </is>
       </c>
     </row>
@@ -30999,7 +30999,7 @@
       <c r="M468" t="inlineStr">
         <is>
           <t>Việc rút nước lũ ở Khu Phố Cũ đã làm lộ ra vô số Tacet Discord. Các Chiến Binh Septimont giờ đây đã mở một cuộc thi săn lùng chúng.
-Đánh bại Tacet Discord trong Khu Vực Challenge và chiếm giữ các Cờ Chinh Phục sẽ tăng Cấp Độ Glory của bạn, mang lại &lt;color=#ffd12f&gt;powerful buffs&lt;/color&gt;. Hãy tận dụng những hiệu ứng này để giành lấy chiến thắng và vinh quang trong thử thách!</t>
+Đánh bại Tacet Discord trong Khu Vực Thử Thách và chiếm giữ các Cờ Chinh Phục sẽ tăng Cấp Độ Vinh Quang của bạn, mang lại &lt;color=#ffd12f&gt;hiệu ứng tăng cường mạnh mẽ&lt;/color&gt;. Hãy tận dụng những hiệu ứng này để giành lấy chiến thắng và vinh quang trong thử thách!</t>
         </is>
       </c>
     </row>
@@ -31064,7 +31064,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Một số Cờ Chinh Phục trong Khu Vực Trial đã bị Tacet Discord chiếm giữ. Hãy đánh bại chúng và chiếm lấy Cờ Chinh Phục để nhận Points Săn và Points Trial. Points Trial sẽ tăng Cấp Độ Trial của cậu. Sau khi đánh bại Tacet Discord, cờ sẽ được chiếm giữ. Khi đã chiếm được, Cờ Chinh Phục sẽ không thể tương tác được nữa.</t>
+          <t>Một số Cờ Chinh Phục trong Khu Vực Thử Thách đã bị Tacet Discord chiếm giữ. Hãy đánh bại chúng và chiếm lấy Cờ Chinh Phục để nhận Điểm Săn và Điểm Thử Thách. Điểm Thử Thách sẽ tăng Cấp Độ Thử Thách của cậu. Sau khi đánh bại Tacet Discord, cờ sẽ được chiếm giữ. Khi đã chiếm được, Cờ Chinh Phục sẽ không thể tương tác được nữa.</t>
         </is>
       </c>
     </row>
@@ -31131,9 +31131,9 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Phản công, Dodge Counter và Tấn Công trong chiến đấu sẽ cấp &lt;color=#ffd12f&gt;Battle Engagement Points&lt;/color&gt;, tạm thời tăng &lt;color=#ffd12f&gt;temporarily raise Glory Levels&lt;/color&gt; lên 100 cấp như Points Săn.
-Khi nhận sát thương, chỉ Cấp Glory tăng từ Battle Engagement Points mới bị giảm, không ảnh hưởng đến Cấp Glory từ Points Săn.
-Cấp Glory tăng từ Battle Engagement Points sẽ giảm nhanh khi rời khỏi chiến đấu.</t>
+          <t>Phản công, Phản đòn né tránh và Tấn Công trong chiến đấu sẽ cấp &lt;color=#ffd12f&gt;Điểm Tham Chiến&lt;/color&gt;, tạm thời tăng &lt;color=#ffd12f&gt;Cấp Vinh Quang&lt;/color&gt; lên 100 cấp như Điểm Săn.
+Khi nhận sát thương, chỉ Cấp Vinh Quang tăng từ Điểm Tham Chiến mới bị giảm, không ảnh hưởng đến Cấp Vinh Quang từ Điểm Săn.
+Cấp Vinh Quang tăng từ Điểm Tham Chiến sẽ giảm nhanh khi rời khỏi chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -31198,7 +31198,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Counterattack có thể Giữ Chân Kerasaur. Nếu Kerasaur bị Giữ Chân lần thứ hai, Tấn Công và Kháng của nó sẽ bị giảm.</t>
+          <t>Phản công có thể Giữ Chân Kerasaur. Nếu Kerasaur bị Giữ Chân lần thứ hai, ATK và Kháng của nó sẽ bị giảm.</t>
         </is>
       </c>
     </row>
@@ -31263,7 +31263,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Dodge nhiều đòn của bọn Drake để giảm Kháng của chúng. Đánh bại một con Drake trong nhóm sẽ khiến chúng không thể phối hợp tấn công.</t>
+          <t>Né nhiều đòn của bọn Drake để giảm Kháng của chúng. Đánh bại một con Drake trong nhóm sẽ khiến chúng không thể phối hợp tấn công.</t>
         </is>
       </c>
     </row>
@@ -31393,7 +31393,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Dodge Counter giúp giảm mạnh Vibration Strength của vỏ Pilgrim's Shell. Tấn công vỏ Pilgrim's Shell bị Hóa Đá sẽ gây Electro DMG lên các mục tiêu trong phạm vi nhất định.</t>
+          <t>Dodge Counter giúp giảm mạnh Sức Rung của vỏ Pilgrim's Shell. Tấn công vỏ Pilgrim's Shell bị Hóa Đá sẽ gây Sát Thương Electro lên các mục tiêu trong phạm vi nhất định.</t>
         </is>
       </c>
     </row>
@@ -31458,7 +31458,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Hero's Legacy Armor sẽ mở khóa Kỹ Năng &lt;color=#ffd12f&gt;Hero's Slash&lt;/color&gt; trong một số tình huống nhất định khi kẻ địch ở trạng thái đặc biệt. Sử dụng kỹ năng này để tiêu diệt hoặc làm suy yếu kẻ địch ngay lập tức.</t>
+          <t>Bộ Giáp Di Sản Anh Hùng sẽ mở khóa Kỹ Năng &lt;color=#ffd12f&gt;Vết Rạch Anh Hùng&lt;/color&gt; trong một số tình huống nhất định khi kẻ địch ở trạng thái đặc biệt. Sử dụng kỹ năng này để tiêu diệt hoặc làm suy yếu kẻ địch ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -31523,7 +31523,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Aim vào cơ cấu, rồi nhấn nút được đánh dấu để mặc Giáp Di Sản Anh Hùng và nhận Kỹ Năng &lt;color=#ffd12f&gt;Hero's Slash&lt;/color&gt;. Aim và {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút tương ứng để chém.</t>
+          <t>Ngắm vào cơ cấu, rồi nhấn nút được đánh dấu để mặc Giáp Di Sản Anh Hùng và nhận Kỹ Năng &lt;color=#ffd12f&gt;Chém Anh Hùng&lt;/color&gt;. Ngắm và {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút tương ứng để chém.</t>
         </is>
       </c>
     </row>
@@ -31653,7 +31653,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Thu thập ba Ký Ức Anh Hùng để nạp năng lượng cho Hero's Legacy Armor. Khi bộ giáp được nạp đầy, hãy nhắm vào cơ cấu và {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút được đánh dấu để mặc Hero's Legacy Armor và sử dụng kỹ năng &lt;color=#ffd12f&gt;Hero's Rend&lt;/color&gt; mạnh mẽ.</t>
+          <t>Thu thập ba Ký Ức Anh Hùng để nạp năng lượng cho Bộ Giáp Di Sản Anh Hùng. Khi bộ giáp được nạp đầy, hãy nhắm vào cơ cấu và {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút được đánh dấu để mặc Bộ Giáp Di Sản Anh Hùng và sử dụng kỹ năng &lt;color=#ffd12f&gt;Hero's Rend&lt;/color&gt; mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Một số Tactical Hologram: Vitreum Dancer có hiệu ứng làm chậm. Trong thử thách Hologram, sẽ xuất hiện những vùng gây giảm tốc độ đáng kể cho cậu.</t>
+          <t>Một số Hologram Chiến Thuật: Vũ Công Vitreum có hiệu ứng làm chậm. Trong thử thách Hologram, sẽ xuất hiện những vùng gây giảm tốc độ đáng kể cho cậu.</t>
         </is>
       </c>
     </row>
@@ -31789,10 +31789,10 @@
       <c r="M480" t="inlineStr">
         <is>
           <t>Mỗi Bản Giao Hưởng có bốn chỉ số cơ bản.
-Strength (STR): Ảnh hưởng đến sát thương gây ra trong Battle Stage.
-Thể Chất (CON): Thể hiện khả năng chịu sát thương của Bản Giao Hưởng.
-Chi Phí Năng Lượng (Cost): Đại diện cho Năng Lượng cần thiết để Triển khai hoặc Điều Chỉnh Bản Giao Hưởng này.
-Sát Thương (DMG): Khi kết thúc mỗi Battle Stage, các Bản Giao Hưởng còn sống sẽ gây sát thương cho đối thủ bằng giá trị này.
+Sức Mạnh (STR): Ảnh hưởng đến DMG gây ra trong Giai Đoạn Chiến Đấu.
+Thể Chất (CON): Thể hiện khả năng chịu DMG của Bản Giao Hưởng.
+Chi Phí Năng Lượng (Cost): Đại diện cho Năng Lượng cần thiết để Triển Khai hoặc Điều Chỉnh Bản Giao Hưởng này.
+Sát Thương (DMG): Khi kết thúc mỗi Giai Đoạn Chiến Đấu, các Bản Giao Hưởng còn sống sẽ gây DMG cho đối thủ bằng giá trị này.
 Nói chung, chỉ số càng cao thì sức mạnh càng lớn.</t>
         </is>
       </c>
@@ -31859,7 +31859,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Những Bản Sao Triệu Hồi sống sót qua Battle Stage sẽ gây sát thương lên đối thủ bằng tổng &lt;color=#ffd12f&gt;DMG&lt;/color&gt; của tất cả chúng. Một số Skills Bản Sao cũng có thể ảnh hưởng đến lượng sát thương mà chúng gây ra.
+          <t>Những Bản Sao Triệu Hồi sống sót qua Giai Đoạn Chiến Đấu sẽ gây DMG lên đối thủ bằng tổng &lt;color=#ffd12f&gt;Sát Thương&lt;/color&gt; của tất cả chúng. Một số Kỹ Năng Bản Sao cũng có thể ảnh hưởng đến lượng DMG mà chúng gây ra.
 Mỗi trận đấu kéo dài tối đa 8 hiệp. Sau hiệp thứ 8, người chơi có nhiều HP hơn sẽ thắng.</t>
         </is>
       </c>
@@ -31991,8 +31991,8 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Một số Echoes sở hữu Kỹ Năng &lt;color=#ffd12f&gt;Biến Đổi&lt;/color&gt; đặc biệt.
-Kéo Echoes có Kỹ Năng &lt;color=#ffd12f&gt;Biến Đổi&lt;/color&gt; vào Khu Vực Biến Hình để kích hoạt. Tuy nhiên, Echoes đó sẽ bị tiêu hao và cậu không thể rút nó ra trong suốt trận đấu.</t>
+          <t>Một số Echo sở hữu Kỹ Năng &lt;color=#ffd12f&gt;Biến Hình&lt;/color&gt; đặc biệt.
+Kéo Echo có Kỹ Năng &lt;color=#ffd12f&gt;Biến Hình&lt;/color&gt; vào Khu Vực Biến Hình để kích hoạt. Tuy nhiên, Echo đó sẽ bị tiêu hao và cậu không thể rút nó ra trong suốt trận đấu.</t>
         </is>
       </c>
     </row>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Sau khi Điều Chỉnh, Echo A sẽ thay thế Echo B trong Vùng Triển Khai, kế thừa sát thương của Echo B (sát thương kế thừa sẽ cộng vào sát thương gốc của Echo A). Echo B sẽ được xáo lại vào bộ bài sau Điều Chỉnh và có thể được rút lại trong các lượt sau.</t>
+          <t>Sau khi Điều Chỉnh, Echo A sẽ thay thế Echo B trong Vùng Triển Khai, kế thừa DMG của Echo B (DMG kế thừa sẽ cộng vào DMG gốc của Echo A). Echo B sẽ được xáo lại vào bộ bài sau Điều Chỉnh và có thể được rút lại trong các lượt sau.</t>
         </is>
       </c>
     </row>
@@ -32122,7 +32122,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Một số Echoes sở hữu Kỹ Năng Special chỉ kích hoạt trong những điều kiện nhất định.</t>
+          <t>Một số Echo sở hữu Kỹ Năng Đặc Biệt chỉ kích hoạt trong những điều kiện nhất định.</t>
         </is>
       </c>
     </row>
@@ -32188,7 +32188,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Khi Resonators bước vào &lt;color=#ffd12f&gt;Sea of Flames&lt;/color&gt;, họ sẽ bị bào mòn bởi Phấn Hoa Incinero, khiến &lt;color=#ffd12f&gt;steady decline in their HP&lt;/color&gt;.
+          <t>Khi Resonator bước vào &lt;color=#ffd12f&gt;Biển Lửa&lt;/color&gt;, họ sẽ bị bào mòn bởi Phấn Hoa Incinero, khiến &lt;color=#ffd12f&gt;HP dần suy giảm&lt;/color&gt;.
 Hiệu ứng này sẽ dần biến mất trong vài giây sau khi ngừng tiếp xúc.</t>
         </is>
       </c>
@@ -32257,7 +32257,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Resonators có thể dùng &lt;color=#ffd12f&gt;Shooting Mechanism&lt;/color&gt; để rèn luyện kỹ năng. Bắn trúng các mục tiêu khác nhau sẽ kích hoạt hiệu ứng khác nhau:
+          <t>Resonator có thể dùng &lt;color=#ffd12f&gt;Cơ Chế Bắn&lt;/color&gt; để rèn luyện kỹ năng. Bắn trúng các mục tiêu khác nhau sẽ kích hoạt hiệu ứng khác nhau:
 Mục tiêu thường: Màu vàng. Bắn trúng tất cả để qua giai đoạn tiếp theo.
 Mục tiêu nổ: Có biểu tượng nổ. Khi trúng, sẽ kích nổ và phá hủy các mục tiêu xung quanh.
 Mục tiêu bẫy: Có biểu tượng cấm. Khi trúng, điểm của bạn sẽ bị trừ.</t>
@@ -32326,8 +32326,8 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Sau khi mở khóa Công cụ, bạn có thể dùng Bộ Nâng để Dodgem &lt;color=#ffd12f&gt;Explosive Spear&lt;/color&gt; vào kẻ địch, gây sát thương diện rộng nhiều giai đoạn.
-Hãy tiêu diệt tất cả Tacet Discord và bảo vệ ba Sound Emulator để hoàn thành thử thách.</t>
+          <t>Sau khi mở khóa Tiện Ích, bạn có thể dùng Bộ Nâng để ném &lt;color=#ffd12f&gt;Giáo Nổ&lt;/color&gt; vào kẻ địch, gây DMG diện rộng nhiều giai đoạn.
+Hãy tiêu diệt tất cả Tacet Discord và bảo vệ ba Bộ Mô Phỏng Âm Thanh để hoàn thành thử thách.</t>
         </is>
       </c>
     </row>
@@ -32392,7 +32392,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Bạn có thể trang bị &lt;color=#ffd12f&gt;Ultrasonic Pulse Chip&lt;/color&gt; để phóng một vòng xoáy nước. Vòng xoáy nước có thể &lt;color=#ffd12f&gt;clear&lt;/color&gt; bùn trên đường đi. Khi trúng kẻ địch, nó sẽ &lt;color=#ffd12f&gt;remove&lt;/color&gt; &lt;color=#ffd12f&gt;Mud Shields&lt;/color&gt; của chúng và đẩy lùi chúng. Khi trúng Swamp Vortex, nó có thể kích hoạt &lt;color=#ffd12f&gt;AoE DMG&lt;/color&gt;.</t>
+          <t>Bạn có thể trang bị &lt;color=#ffd12f&gt;Chip Xung Siêu Âm&lt;/color&gt; để phóng một vòng xoáy nước. Vòng xoáy nước có thể &lt;color=#ffd12f&gt;dọn sạch&lt;/color&gt; bùn trên đường đi. Khi trúng kẻ địch, nó sẽ &lt;color=#ffd12f&gt;phá hủy&lt;/color&gt; &lt;color=#ffd12f&gt;Khiên Bùn&lt;/color&gt; của chúng và đẩy lùi chúng. Khi trúng Swamp Vortex, nó có thể kích hoạt &lt;color=#ffd12f&gt;Sát Thương Khu Vực&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32457,7 +32457,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Xoáy Lầy &lt;color=#ffd12f&gt;knocks back&lt;/color&gt; các đơn vị bị trúng và gây &lt;color=#ffd12f&gt;minor damage&lt;/color&gt;. Xoáy Nước do Ultrasonic Pulse Chip tạo ra có thể xóa bỏ Xoáy Lầy, đồng thời gây &lt;color=#ffd12f&gt;a large amount of damage&lt;/color&gt; cho kẻ địch trong phạm vi.</t>
+          <t>Xoáy Lầy &lt;color=#ffd12f&gt;đẩy lùi&lt;/color&gt; các đơn vị bị trúng và gây &lt;color=#ffd12f&gt;sát thương nhẹ&lt;/color&gt;. Xoáy Nước do Chip Xung Siêu Âm tạo ra có thể xóa bỏ Xoáy Lầy, đồng thời gây &lt;color=#ffd12f&gt;sát thương lớn&lt;/color&gt; cho kẻ địch trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -32522,7 +32522,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt Suppressor, cậu phải &lt;color=#ffd12f&gt;remain within its range for a period of time&lt;/color&gt; để tiến hành sửa chữa. Khi &lt;color=#ffd12f&gt;mud&lt;/color&gt; và &lt;color=#ffd12f&gt;enemies&lt;/color&gt; xuất hiện trong phạm vi, Suppressor sẽ ngừng hoạt động.</t>
+          <t>Sau khi kích hoạt Suppressor, cậu phải &lt;color=#ffd12f&gt;ở trong phạm vi của nó một khoảng thời gian&lt;/color&gt; để tiến hành sửa chữa. Khi &lt;color=#ffd12f&gt;bùn&lt;/color&gt; và &lt;color=#ffd12f&gt;kẻ địch&lt;/color&gt; xuất hiện trong phạm vi, Suppressor sẽ ngừng hoạt động.</t>
         </is>
       </c>
     </row>
@@ -32587,7 +32587,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Mud &lt;color=#ffd12f&gt;blocks the mechanisms and grants the enemies special Mud Shields&lt;/color&gt;. Xoáy Nước từ Ultrasonic Pulse Chip và Xoáy Đầm Lầy có thể cuốn trôi bùn và phá bỏ khiên.</t>
+          <t>Bùn đất &lt;color=#ffd12f&gt;làm kẹt cơ cấu và tạo khiên Bùn Đặc Biệt cho kẻ địch&lt;/color&gt;. Xoáy Nước từ Chip Xung Siêu Âm và Xoáy Đầm Lầy có thể cuốn trôi bùn và phá bỏ khiên.</t>
         </is>
       </c>
     </row>
@@ -32653,8 +32653,8 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Sensor
-Sensor có thể phát hiện nội dung giá trị trong một phạm vi nhất định, như &lt;color=#b49f50&gt;collectible items, enemy weaknesses or Acoustic Prints&lt;/color&gt;.</t>
+          <t>Cảm Biến
+Cảm Biến có thể phát hiện nội dung giá trị trong một phạm vi nhất định, như &lt;color=#b49f50&gt;vật phẩm thu thập, điểm yếu của kẻ địch hoặc Dấu Âm Thanh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32720,8 +32720,8 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Levitator
-Thiết bị này cho phép cậu điều khiển các vật thể được đánh dấu và Dodgem chúng vào mục tiêu cụ thể để tạo ra những hiệu ứng khác nhau. Hãy dùng nó để thu giữ và thao tác với các vật thể khi cần.</t>
+          <t>Thiết bị điều khiển bay
+Thiết bị này cho phép cậu điều khiển các vật thể được đánh dấu và ném chúng vào mục tiêu cụ thể để tạo ra những hiệu ứng khác nhau. Hãy dùng nó để thu giữ và thao tác với các vật thể khi cần.</t>
         </is>
       </c>
     </row>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt Resonance Beacon, cậu có thể mở Map và dịch chuyển nhanh đến Resonance Beacon đã kích hoạt.</t>
+          <t>Sau khi kích hoạt Resonance Beacon, cậu có thể mở Bản Đồ và dịch chuyển nhanh đến Resonance Beacon đã kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -32851,7 +32851,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Nexus Resonance lưu trữ thông tin về khu vực xung quanh. Kích hoạt để nhận dữ liệu Map tương ứng.</t>
+          <t>Nexus Cộng Hưởng lưu trữ thông tin về khu vực xung quanh. Kích hoạt để nhận dữ liệu Bản Đồ tương ứng.</t>
         </is>
       </c>
     </row>
@@ -32916,7 +32916,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Đến Trạm Resonance để &lt;color=#ffd12f&gt;heal&lt;/color&gt; Resonators bị thương hoặc bất tỉnh.</t>
+          <t>Đến Trạm Cộng Hưởng để &lt;color=#ffd12f&gt;hồi phục&lt;/color&gt; Resonator bị thương hoặc bất tỉnh.</t>
         </is>
       </c>
     </row>
@@ -32982,8 +32982,8 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Các Resonators bị thương hoặc ngã gục có thể tập trung tại &lt;color=#b49f50&gt;Resonance Nexus&lt;/color&gt; để hồi phục về trạng thái tốt nhất. 
-Nếu tạm thời không thể đến Nút Resonance gần nhất, bạn có thể &lt;color=#b49f50&gt;Cook&lt;/color&gt; và dùng thức ăn để khôi phục HP cho Resonators.</t>
+          <t>Các Resonator bị thương hoặc ngã gục có thể tập trung tại &lt;color=#b49f50&gt;Nút Cộng Hưởng&lt;/color&gt; để hồi phục về trạng thái tốt nhất. 
+Nếu tạm thời không thể đến Nút Cộng Hưởng gần nhất, bạn có thể &lt;color=#b49f50&gt;Nấu ăn&lt;/color&gt; và dùng thức ăn để khôi phục HP cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -33048,7 +33048,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Terminal Resonance lưu giữ dữ liệu kẻ địch liên quan. Sử dụng &lt;color=#b49f50&gt;Sensor&lt;/color&gt; tích hợp để phát hiện &lt;color=#b49f50&gt;Weaknesses&lt;/color&gt; của kẻ địch. Attack vào điểm yếu bằng các phương pháp phù hợp sẽ gây thêm sát thương.</t>
+          <t>Thiết bị đầu cuối Cộng Hưởng lưu giữ dữ liệu kẻ địch liên quan. Sử dụng &lt;color=#b49f50&gt;Cảm Biến&lt;/color&gt; tích hợp để phát hiện &lt;color=#b49f50&gt;Điểm Yếu&lt;/color&gt; của kẻ địch. Tấn công vào điểm yếu bằng các phương pháp phù hợp sẽ gây thêm sát thương.</t>
         </is>
       </c>
     </row>
@@ -33113,7 +33113,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Khi đạt đến giới hạn Cấp Liên Minh nhất định, cậu sẽ cần hoàn thành Nhiệm Vụ Thăng Hoa để tăng SOL3 Giai đoạn của mình.</t>
+          <t>Khi đạt đến giới hạn Cấp Liên Minh nhất định, cậu sẽ cần hoàn thành Nhiệm Vụ Thăng Hoa để tăng Giai Đoạn SOL3 của mình.</t>
         </is>
       </c>
     </row>
